--- a/data/JLL.xlsx
+++ b/data/JLL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG armazem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D408D75B-93AD-4421-BB45-D82DD6B7617F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787D13B1-5380-45AE-AC65-102C5C8D81D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JLL" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="152">
   <si>
     <t>% Cumprimento de Jornada</t>
   </si>
@@ -450,13 +450,52 @@
   </si>
   <si>
     <t>LUANA NASCIMENTO BATISTA</t>
+  </si>
+  <si>
+    <t>ELIRIANE DE FREITAS</t>
+  </si>
+  <si>
+    <t>JUCI VICENTE BARBOZA</t>
+  </si>
+  <si>
+    <t>SUIANI VAZ DA CUNHA</t>
+  </si>
+  <si>
+    <t>TATIANE VIRGINIA PETROCHINSKI</t>
+  </si>
+  <si>
+    <t>ARNALDO IENK</t>
+  </si>
+  <si>
+    <t>BRUNO DA SILVA ALMEIDA</t>
+  </si>
+  <si>
+    <t>CLAYTON ANANIAS PEREIRA</t>
+  </si>
+  <si>
+    <t>DHAYMON DOMINGOS E SILVA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL ORTIZ CARACAS</t>
+  </si>
+  <si>
+    <t>NEIVERALDO DELLA TORRES</t>
+  </si>
+  <si>
+    <t>RAFAEL WILLIAN DE ANDRADE</t>
+  </si>
+  <si>
+    <t>RONI CRISTIAN COSTA ROSA</t>
+  </si>
+  <si>
+    <t>WILIAM JARDEL DE MELO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -465,6 +504,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -505,7 +550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -515,6 +560,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -829,12 +875,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C278"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:C409"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="5" width="27.140625" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="5" width="27.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3893,6 +3939,1444 @@
         <v>46054</v>
       </c>
     </row>
+    <row r="279" spans="1:3">
+      <c r="A279" t="s">
+        <v>1</v>
+      </c>
+      <c r="B279" s="9">
+        <v>1</v>
+      </c>
+      <c r="C279" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" t="s">
+        <v>121</v>
+      </c>
+      <c r="B280" s="5">
+        <v>1</v>
+      </c>
+      <c r="C280" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
+        <v>12</v>
+      </c>
+      <c r="B281" s="5">
+        <v>1</v>
+      </c>
+      <c r="C281" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" t="s">
+        <v>13</v>
+      </c>
+      <c r="B282" s="5">
+        <v>1</v>
+      </c>
+      <c r="C282" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283" t="s">
+        <v>20</v>
+      </c>
+      <c r="B283" s="5">
+        <v>1</v>
+      </c>
+      <c r="C283" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" t="s">
+        <v>21</v>
+      </c>
+      <c r="B284" s="5">
+        <v>1</v>
+      </c>
+      <c r="C284" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" t="s">
+        <v>14</v>
+      </c>
+      <c r="B285" s="5">
+        <v>1</v>
+      </c>
+      <c r="C285" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" t="s">
+        <v>15</v>
+      </c>
+      <c r="B286" s="5">
+        <v>1</v>
+      </c>
+      <c r="C286" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" t="s">
+        <v>16</v>
+      </c>
+      <c r="B287" s="5">
+        <v>1</v>
+      </c>
+      <c r="C287" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" t="s">
+        <v>17</v>
+      </c>
+      <c r="B288" s="5">
+        <v>1</v>
+      </c>
+      <c r="C288" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" t="s">
+        <v>19</v>
+      </c>
+      <c r="B289" s="5">
+        <v>1</v>
+      </c>
+      <c r="C289" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" t="s">
+        <v>1</v>
+      </c>
+      <c r="B290" s="9">
+        <v>1</v>
+      </c>
+      <c r="C290" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" t="s">
+        <v>113</v>
+      </c>
+      <c r="B291" s="5">
+        <v>1</v>
+      </c>
+      <c r="C291" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292" t="s">
+        <v>1</v>
+      </c>
+      <c r="B292" s="9">
+        <v>1</v>
+      </c>
+      <c r="C292" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293" t="s">
+        <v>111</v>
+      </c>
+      <c r="B293" s="5">
+        <v>1</v>
+      </c>
+      <c r="C293" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" t="s">
+        <v>138</v>
+      </c>
+      <c r="B294" s="5">
+        <v>1</v>
+      </c>
+      <c r="C294" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295" t="s">
+        <v>137</v>
+      </c>
+      <c r="B295" s="5">
+        <v>1</v>
+      </c>
+      <c r="C295" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" t="s">
+        <v>1</v>
+      </c>
+      <c r="B296" s="9">
+        <v>1</v>
+      </c>
+      <c r="C296" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297" t="s">
+        <v>2</v>
+      </c>
+      <c r="B297" s="5">
+        <v>1</v>
+      </c>
+      <c r="C297" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" t="s">
+        <v>120</v>
+      </c>
+      <c r="B298" s="5">
+        <v>1</v>
+      </c>
+      <c r="C298" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" t="s">
+        <v>3</v>
+      </c>
+      <c r="B299" s="5">
+        <v>1</v>
+      </c>
+      <c r="C299" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" t="s">
+        <v>4</v>
+      </c>
+      <c r="B300" s="5">
+        <v>1</v>
+      </c>
+      <c r="C300" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" t="s">
+        <v>5</v>
+      </c>
+      <c r="B301" s="5">
+        <v>1</v>
+      </c>
+      <c r="C301" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" t="s">
+        <v>7</v>
+      </c>
+      <c r="B302" s="5">
+        <v>1</v>
+      </c>
+      <c r="C302" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" t="s">
+        <v>9</v>
+      </c>
+      <c r="B303" s="5">
+        <v>1</v>
+      </c>
+      <c r="C303" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" t="s">
+        <v>10</v>
+      </c>
+      <c r="B304" s="5">
+        <v>1</v>
+      </c>
+      <c r="C304" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
+        <v>11</v>
+      </c>
+      <c r="B305" s="5">
+        <v>1</v>
+      </c>
+      <c r="C305" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" t="s">
+        <v>1</v>
+      </c>
+      <c r="B306" s="9">
+        <v>1</v>
+      </c>
+      <c r="C306" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" t="s">
+        <v>112</v>
+      </c>
+      <c r="B307" s="5">
+        <v>1</v>
+      </c>
+      <c r="C307" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" t="s">
+        <v>1</v>
+      </c>
+      <c r="B308" s="9">
+        <v>1</v>
+      </c>
+      <c r="C308" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" t="s">
+        <v>87</v>
+      </c>
+      <c r="B309" s="5">
+        <v>1</v>
+      </c>
+      <c r="C309" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310" t="s">
+        <v>1</v>
+      </c>
+      <c r="B310" s="9">
+        <v>1</v>
+      </c>
+      <c r="C310" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" t="s">
+        <v>114</v>
+      </c>
+      <c r="B311" s="5">
+        <v>1</v>
+      </c>
+      <c r="C311" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" t="s">
+        <v>1</v>
+      </c>
+      <c r="B312" s="9">
+        <v>1</v>
+      </c>
+      <c r="C312" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313" t="s">
+        <v>117</v>
+      </c>
+      <c r="B313" s="5">
+        <v>1</v>
+      </c>
+      <c r="C313" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" t="s">
+        <v>1</v>
+      </c>
+      <c r="B314" s="9">
+        <v>0.99512987012987009</v>
+      </c>
+      <c r="C314" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" t="s">
+        <v>22</v>
+      </c>
+      <c r="B315" s="5">
+        <v>1</v>
+      </c>
+      <c r="C315" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316" t="s">
+        <v>23</v>
+      </c>
+      <c r="B316" s="5">
+        <v>1</v>
+      </c>
+      <c r="C316" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" t="s">
+        <v>122</v>
+      </c>
+      <c r="B317" s="5">
+        <v>1</v>
+      </c>
+      <c r="C317" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" t="s">
+        <v>24</v>
+      </c>
+      <c r="B318" s="5">
+        <v>1</v>
+      </c>
+      <c r="C318" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" t="s">
+        <v>25</v>
+      </c>
+      <c r="B319" s="5">
+        <v>1</v>
+      </c>
+      <c r="C319" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" t="s">
+        <v>123</v>
+      </c>
+      <c r="B320" s="5">
+        <v>1</v>
+      </c>
+      <c r="C320" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" t="s">
+        <v>27</v>
+      </c>
+      <c r="B321" s="5">
+        <v>1</v>
+      </c>
+      <c r="C321" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" t="s">
+        <v>124</v>
+      </c>
+      <c r="B322" s="5">
+        <v>1</v>
+      </c>
+      <c r="C322" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" t="s">
+        <v>125</v>
+      </c>
+      <c r="B323" s="5">
+        <v>1</v>
+      </c>
+      <c r="C323" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" t="s">
+        <v>126</v>
+      </c>
+      <c r="B324" s="5">
+        <v>1</v>
+      </c>
+      <c r="C324" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
+        <v>139</v>
+      </c>
+      <c r="B325" s="5">
+        <v>1</v>
+      </c>
+      <c r="C325" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" t="s">
+        <v>128</v>
+      </c>
+      <c r="B326" s="5">
+        <v>1</v>
+      </c>
+      <c r="C326" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" t="s">
+        <v>140</v>
+      </c>
+      <c r="B327" s="5">
+        <v>1</v>
+      </c>
+      <c r="C327" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" t="s">
+        <v>129</v>
+      </c>
+      <c r="B328" s="5">
+        <v>1</v>
+      </c>
+      <c r="C328" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" t="s">
+        <v>32</v>
+      </c>
+      <c r="B329" s="5">
+        <v>1</v>
+      </c>
+      <c r="C329" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" t="s">
+        <v>34</v>
+      </c>
+      <c r="B330" s="5">
+        <v>1</v>
+      </c>
+      <c r="C330" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" t="s">
+        <v>130</v>
+      </c>
+      <c r="B331" s="5">
+        <v>1</v>
+      </c>
+      <c r="C331" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" t="s">
+        <v>131</v>
+      </c>
+      <c r="B332" s="5">
+        <v>1</v>
+      </c>
+      <c r="C332" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" t="s">
+        <v>35</v>
+      </c>
+      <c r="B333" s="5">
+        <v>1</v>
+      </c>
+      <c r="C333" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" t="s">
+        <v>36</v>
+      </c>
+      <c r="B334" s="5">
+        <v>1</v>
+      </c>
+      <c r="C334" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" t="s">
+        <v>43</v>
+      </c>
+      <c r="B335" s="5">
+        <v>1</v>
+      </c>
+      <c r="C335" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" t="s">
+        <v>38</v>
+      </c>
+      <c r="B336" s="5">
+        <v>1</v>
+      </c>
+      <c r="C336" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" t="s">
+        <v>132</v>
+      </c>
+      <c r="B337" s="5">
+        <v>1</v>
+      </c>
+      <c r="C337" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" t="s">
+        <v>39</v>
+      </c>
+      <c r="B338" s="5">
+        <v>1</v>
+      </c>
+      <c r="C338" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" t="s">
+        <v>46</v>
+      </c>
+      <c r="B339" s="5">
+        <v>1</v>
+      </c>
+      <c r="C339" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" t="s">
+        <v>40</v>
+      </c>
+      <c r="B340" s="5">
+        <v>1</v>
+      </c>
+      <c r="C340" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" t="s">
+        <v>141</v>
+      </c>
+      <c r="B341" s="5">
+        <v>1</v>
+      </c>
+      <c r="C341" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" t="s">
+        <v>142</v>
+      </c>
+      <c r="B342" s="5">
+        <v>1</v>
+      </c>
+      <c r="C342" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" t="s">
+        <v>41</v>
+      </c>
+      <c r="B343" s="5">
+        <v>1</v>
+      </c>
+      <c r="C343" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344" t="s">
+        <v>42</v>
+      </c>
+      <c r="B344" s="5">
+        <v>1</v>
+      </c>
+      <c r="C344" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345" t="s">
+        <v>18</v>
+      </c>
+      <c r="B345" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="C345" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346" t="s">
+        <v>133</v>
+      </c>
+      <c r="B346" s="5">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="C346" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347" t="s">
+        <v>1</v>
+      </c>
+      <c r="B347" s="9">
+        <v>0.99358974358974361</v>
+      </c>
+      <c r="C347" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348" t="s">
+        <v>103</v>
+      </c>
+      <c r="B348" s="5">
+        <v>1</v>
+      </c>
+      <c r="C348" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349" t="s">
+        <v>109</v>
+      </c>
+      <c r="B349" s="5">
+        <v>1</v>
+      </c>
+      <c r="C349" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" t="s">
+        <v>104</v>
+      </c>
+      <c r="B350" s="5">
+        <v>1</v>
+      </c>
+      <c r="C350" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" t="s">
+        <v>47</v>
+      </c>
+      <c r="B351" s="5">
+        <v>1</v>
+      </c>
+      <c r="C351" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" t="s">
+        <v>106</v>
+      </c>
+      <c r="B352" s="5">
+        <v>1</v>
+      </c>
+      <c r="C352" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" t="s">
+        <v>107</v>
+      </c>
+      <c r="B353" s="5">
+        <v>1</v>
+      </c>
+      <c r="C353" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" t="s">
+        <v>108</v>
+      </c>
+      <c r="B354" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C354" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" t="s">
+        <v>1</v>
+      </c>
+      <c r="B355" s="9">
+        <v>0.99081632653061225</v>
+      </c>
+      <c r="C355" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" t="s">
+        <v>86</v>
+      </c>
+      <c r="B356" s="5">
+        <v>1</v>
+      </c>
+      <c r="C356" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" t="s">
+        <v>48</v>
+      </c>
+      <c r="B357" s="5">
+        <v>1</v>
+      </c>
+      <c r="C357" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358" t="s">
+        <v>143</v>
+      </c>
+      <c r="B358" s="5">
+        <v>1</v>
+      </c>
+      <c r="C358" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359" t="s">
+        <v>50</v>
+      </c>
+      <c r="B359" s="5">
+        <v>1</v>
+      </c>
+      <c r="C359" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360" t="s">
+        <v>144</v>
+      </c>
+      <c r="B360" s="5">
+        <v>1</v>
+      </c>
+      <c r="C360" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" t="s">
+        <v>51</v>
+      </c>
+      <c r="B361" s="5">
+        <v>1</v>
+      </c>
+      <c r="C361" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" t="s">
+        <v>52</v>
+      </c>
+      <c r="B362" s="5">
+        <v>1</v>
+      </c>
+      <c r="C362" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363" t="s">
+        <v>53</v>
+      </c>
+      <c r="B363" s="5">
+        <v>1</v>
+      </c>
+      <c r="C363" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" t="s">
+        <v>145</v>
+      </c>
+      <c r="B364" s="5">
+        <v>1</v>
+      </c>
+      <c r="C364" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365" t="s">
+        <v>146</v>
+      </c>
+      <c r="B365" s="5">
+        <v>1</v>
+      </c>
+      <c r="C365" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366" t="s">
+        <v>57</v>
+      </c>
+      <c r="B366" s="5">
+        <v>1</v>
+      </c>
+      <c r="C366" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367" t="s">
+        <v>92</v>
+      </c>
+      <c r="B367" s="5">
+        <v>1</v>
+      </c>
+      <c r="C367" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368" t="s">
+        <v>59</v>
+      </c>
+      <c r="B368" s="5">
+        <v>1</v>
+      </c>
+      <c r="C368" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369" t="s">
+        <v>60</v>
+      </c>
+      <c r="B369" s="5">
+        <v>1</v>
+      </c>
+      <c r="C369" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370" t="s">
+        <v>62</v>
+      </c>
+      <c r="B370" s="5">
+        <v>1</v>
+      </c>
+      <c r="C370" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" t="s">
+        <v>63</v>
+      </c>
+      <c r="B371" s="5">
+        <v>1</v>
+      </c>
+      <c r="C371" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372" t="s">
+        <v>64</v>
+      </c>
+      <c r="B372" s="5">
+        <v>1</v>
+      </c>
+      <c r="C372" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373" t="s">
+        <v>66</v>
+      </c>
+      <c r="B373" s="5">
+        <v>1</v>
+      </c>
+      <c r="C373" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374" t="s">
+        <v>67</v>
+      </c>
+      <c r="B374" s="5">
+        <v>1</v>
+      </c>
+      <c r="C374" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375" t="s">
+        <v>147</v>
+      </c>
+      <c r="B375" s="5">
+        <v>1</v>
+      </c>
+      <c r="C375" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" t="s">
+        <v>89</v>
+      </c>
+      <c r="B376" s="5">
+        <v>1</v>
+      </c>
+      <c r="C376" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" t="s">
+        <v>94</v>
+      </c>
+      <c r="B377" s="5">
+        <v>1</v>
+      </c>
+      <c r="C377" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" t="s">
+        <v>70</v>
+      </c>
+      <c r="B378" s="5">
+        <v>1</v>
+      </c>
+      <c r="C378" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" t="s">
+        <v>134</v>
+      </c>
+      <c r="B379" s="5">
+        <v>1</v>
+      </c>
+      <c r="C379" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" t="s">
+        <v>90</v>
+      </c>
+      <c r="B380" s="5">
+        <v>1</v>
+      </c>
+      <c r="C380" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" t="s">
+        <v>71</v>
+      </c>
+      <c r="B381" s="5">
+        <v>1</v>
+      </c>
+      <c r="C381" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" t="s">
+        <v>73</v>
+      </c>
+      <c r="B382" s="5">
+        <v>1</v>
+      </c>
+      <c r="C382" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" t="s">
+        <v>87</v>
+      </c>
+      <c r="B383" s="5">
+        <v>1</v>
+      </c>
+      <c r="C383" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384" t="s">
+        <v>135</v>
+      </c>
+      <c r="B384" s="5">
+        <v>1</v>
+      </c>
+      <c r="C384" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385" t="s">
+        <v>74</v>
+      </c>
+      <c r="B385" s="5">
+        <v>1</v>
+      </c>
+      <c r="C385" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386" t="s">
+        <v>76</v>
+      </c>
+      <c r="B386" s="5">
+        <v>1</v>
+      </c>
+      <c r="C386" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387" t="s">
+        <v>148</v>
+      </c>
+      <c r="B387" s="5">
+        <v>1</v>
+      </c>
+      <c r="C387" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" t="s">
+        <v>98</v>
+      </c>
+      <c r="B388" s="5">
+        <v>1</v>
+      </c>
+      <c r="C388" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" t="s">
+        <v>99</v>
+      </c>
+      <c r="B389" s="5">
+        <v>1</v>
+      </c>
+      <c r="C389" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" t="s">
+        <v>149</v>
+      </c>
+      <c r="B390" s="5">
+        <v>1</v>
+      </c>
+      <c r="C390" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391" t="s">
+        <v>102</v>
+      </c>
+      <c r="B391" s="5">
+        <v>1</v>
+      </c>
+      <c r="C391" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" t="s">
+        <v>79</v>
+      </c>
+      <c r="B392" s="5">
+        <v>1</v>
+      </c>
+      <c r="C392" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393" t="s">
+        <v>150</v>
+      </c>
+      <c r="B393" s="5">
+        <v>1</v>
+      </c>
+      <c r="C393" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" t="s">
+        <v>136</v>
+      </c>
+      <c r="B394" s="5">
+        <v>1</v>
+      </c>
+      <c r="C394" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" t="s">
+        <v>82</v>
+      </c>
+      <c r="B395" s="5">
+        <v>1</v>
+      </c>
+      <c r="C395" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396" t="s">
+        <v>83</v>
+      </c>
+      <c r="B396" s="5">
+        <v>1</v>
+      </c>
+      <c r="C396" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397" t="s">
+        <v>88</v>
+      </c>
+      <c r="B397" s="5">
+        <v>1</v>
+      </c>
+      <c r="C397" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398" t="s">
+        <v>93</v>
+      </c>
+      <c r="B398" s="5">
+        <v>1</v>
+      </c>
+      <c r="C398" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399" t="s">
+        <v>95</v>
+      </c>
+      <c r="B399" s="5">
+        <v>1</v>
+      </c>
+      <c r="C399" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400" t="s">
+        <v>96</v>
+      </c>
+      <c r="B400" s="5">
+        <v>1</v>
+      </c>
+      <c r="C400" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" t="s">
+        <v>151</v>
+      </c>
+      <c r="B401" s="5">
+        <v>1</v>
+      </c>
+      <c r="C401" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" t="s">
+        <v>97</v>
+      </c>
+      <c r="B402" s="5">
+        <v>1</v>
+      </c>
+      <c r="C402" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" t="s">
+        <v>44</v>
+      </c>
+      <c r="B403" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C403" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3">
+      <c r="A404" t="s">
+        <v>85</v>
+      </c>
+      <c r="B404" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C404" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405" t="s">
+        <v>100</v>
+      </c>
+      <c r="B405" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C405" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" t="s">
+        <v>69</v>
+      </c>
+      <c r="B406" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C406" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407" t="s">
+        <v>49</v>
+      </c>
+      <c r="B407" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C407" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" t="s">
+        <v>84</v>
+      </c>
+      <c r="B408" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="C408" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="B409" s="9">
+        <v>0.99435518888406427</v>
+      </c>
+      <c r="C409" s="8">
+        <v>46082</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/JLL.xlsx
+++ b/data/JLL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG armazem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787D13B1-5380-45AE-AC65-102C5C8D81D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6239B33-19D9-4A7B-A5B9-12386268B7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JLL" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="158">
   <si>
     <t>% Cumprimento de Jornada</t>
   </si>
@@ -489,13 +489,31 @@
   </si>
   <si>
     <t>WILIAM JARDEL DE MELO</t>
+  </si>
+  <si>
+    <t>MARCELO DE MATOS LEAL</t>
+  </si>
+  <si>
+    <t>RUAN DOS SANTOS BUENO</t>
+  </si>
+  <si>
+    <t>CARLOS DANIEL DE SOUZA AUGUSTINHO</t>
+  </si>
+  <si>
+    <t>JAMERSON SCOTT GONCALVES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>JULIO CEZAR RIBEIRO</t>
+  </si>
+  <si>
+    <t>JOAO MARIA MESTRIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -504,6 +522,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -875,15 +894,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C409"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:C533"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.6640625" customWidth="1"/>
     <col min="2" max="5" width="27.109375" customWidth="1"/>
     <col min="9" max="9" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>118</v>
       </c>
@@ -894,7 +913,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="4">
         <v>0.89977528089887637</v>
@@ -903,7 +922,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -914,7 +933,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -925,7 +944,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -936,7 +955,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -947,7 +966,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -958,7 +977,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -969,7 +988,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -980,7 +999,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -991,7 +1010,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1002,7 +1021,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1013,7 +1032,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1024,7 +1043,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
@@ -1035,7 +1054,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -1046,7 +1065,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
@@ -1057,7 +1076,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -1068,7 +1087,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -1079,7 +1098,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -1090,7 +1109,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -1101,7 +1120,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -1112,7 +1131,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -1123,7 +1142,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -1134,7 +1153,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
@@ -1145,7 +1164,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>1</v>
       </c>
@@ -1156,7 +1175,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
@@ -1167,7 +1186,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>23</v>
       </c>
@@ -1178,7 +1197,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -1189,7 +1208,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>25</v>
       </c>
@@ -1200,7 +1219,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
@@ -1211,7 +1230,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
@@ -1222,7 +1241,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
@@ -1233,7 +1252,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -1244,7 +1263,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
@@ -1255,7 +1274,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
@@ -1266,7 +1285,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -1277,7 +1296,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>33</v>
       </c>
@@ -1288,7 +1307,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1318,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>35</v>
       </c>
@@ -1310,7 +1329,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
@@ -1321,7 +1340,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>37</v>
       </c>
@@ -1332,7 +1351,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>38</v>
       </c>
@@ -1343,7 +1362,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
@@ -1354,7 +1373,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>40</v>
       </c>
@@ -1365,7 +1384,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>41</v>
       </c>
@@ -1376,7 +1395,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>42</v>
       </c>
@@ -1387,7 +1406,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
@@ -1398,7 +1417,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>44</v>
       </c>
@@ -1409,7 +1428,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>45</v>
       </c>
@@ -1420,7 +1439,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>46</v>
       </c>
@@ -1431,7 +1450,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>47</v>
       </c>
@@ -1442,7 +1461,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>1</v>
       </c>
@@ -1453,7 +1472,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>48</v>
       </c>
@@ -1464,7 +1483,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>49</v>
       </c>
@@ -1475,7 +1494,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>50</v>
       </c>
@@ -1486,7 +1505,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>51</v>
       </c>
@@ -1497,7 +1516,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>52</v>
       </c>
@@ -1508,7 +1527,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>53</v>
       </c>
@@ -1519,7 +1538,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>54</v>
       </c>
@@ -1530,7 +1549,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>55</v>
       </c>
@@ -1541,7 +1560,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>56</v>
       </c>
@@ -1552,7 +1571,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>57</v>
       </c>
@@ -1563,7 +1582,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>58</v>
       </c>
@@ -1574,7 +1593,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>59</v>
       </c>
@@ -1585,7 +1604,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>60</v>
       </c>
@@ -1596,7 +1615,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>61</v>
       </c>
@@ -1607,7 +1626,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>62</v>
       </c>
@@ -1618,7 +1637,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>63</v>
       </c>
@@ -1629,7 +1648,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>64</v>
       </c>
@@ -1640,7 +1659,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>65</v>
       </c>
@@ -1651,7 +1670,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>66</v>
       </c>
@@ -1662,7 +1681,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>67</v>
       </c>
@@ -1673,7 +1692,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>68</v>
       </c>
@@ -1684,7 +1703,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>69</v>
       </c>
@@ -1695,7 +1714,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>70</v>
       </c>
@@ -1706,7 +1725,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>71</v>
       </c>
@@ -1717,7 +1736,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>72</v>
       </c>
@@ -1728,7 +1747,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>73</v>
       </c>
@@ -1739,7 +1758,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>74</v>
       </c>
@@ -1750,7 +1769,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>75</v>
       </c>
@@ -1761,7 +1780,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>76</v>
       </c>
@@ -1772,7 +1791,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>77</v>
       </c>
@@ -1783,7 +1802,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>78</v>
       </c>
@@ -1794,7 +1813,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>79</v>
       </c>
@@ -1805,7 +1824,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>80</v>
       </c>
@@ -1816,7 +1835,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>81</v>
       </c>
@@ -1827,7 +1846,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>82</v>
       </c>
@@ -1838,7 +1857,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>83</v>
       </c>
@@ -1849,7 +1868,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>84</v>
       </c>
@@ -1860,7 +1879,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>85</v>
       </c>
@@ -1871,7 +1890,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>86</v>
       </c>
@@ -1882,7 +1901,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>87</v>
       </c>
@@ -1893,7 +1912,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>88</v>
       </c>
@@ -1904,7 +1923,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>89</v>
       </c>
@@ -1915,7 +1934,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>90</v>
       </c>
@@ -1926,7 +1945,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>91</v>
       </c>
@@ -1937,7 +1956,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>92</v>
       </c>
@@ -1948,7 +1967,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>93</v>
       </c>
@@ -1959,7 +1978,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>94</v>
       </c>
@@ -1970,7 +1989,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>95</v>
       </c>
@@ -1981,7 +2000,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>96</v>
       </c>
@@ -1992,7 +2011,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>97</v>
       </c>
@@ -2003,7 +2022,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>98</v>
       </c>
@@ -2014,7 +2033,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>99</v>
       </c>
@@ -2025,7 +2044,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>100</v>
       </c>
@@ -2036,7 +2055,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>101</v>
       </c>
@@ -2047,7 +2066,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>102</v>
       </c>
@@ -2058,7 +2077,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>1</v>
       </c>
@@ -2069,7 +2088,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>103</v>
       </c>
@@ -2080,7 +2099,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>104</v>
       </c>
@@ -2091,7 +2110,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>105</v>
       </c>
@@ -2102,7 +2121,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>106</v>
       </c>
@@ -2113,7 +2132,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>107</v>
       </c>
@@ -2124,7 +2143,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>108</v>
       </c>
@@ -2135,7 +2154,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>109</v>
       </c>
@@ -2146,7 +2165,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>1</v>
       </c>
@@ -2157,7 +2176,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>110</v>
       </c>
@@ -2168,7 +2187,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>1</v>
       </c>
@@ -2179,7 +2198,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>111</v>
       </c>
@@ -2190,7 +2209,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>1</v>
       </c>
@@ -2201,7 +2220,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>112</v>
       </c>
@@ -2212,7 +2231,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>1</v>
       </c>
@@ -2223,7 +2242,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>113</v>
       </c>
@@ -2234,7 +2253,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>1</v>
       </c>
@@ -2245,7 +2264,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>114</v>
       </c>
@@ -2256,7 +2275,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>115</v>
       </c>
@@ -2267,7 +2286,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>1</v>
       </c>
@@ -2278,7 +2297,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>116</v>
       </c>
@@ -2289,7 +2308,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>117</v>
       </c>
@@ -2300,7 +2319,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>120</v>
       </c>
@@ -2311,7 +2330,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>3</v>
       </c>
@@ -2322,7 +2341,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>4</v>
       </c>
@@ -2333,7 +2352,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>5</v>
       </c>
@@ -2344,7 +2363,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>6</v>
       </c>
@@ -2355,7 +2374,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>7</v>
       </c>
@@ -2366,7 +2385,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>8</v>
       </c>
@@ -2377,7 +2396,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>9</v>
       </c>
@@ -2388,7 +2407,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>10</v>
       </c>
@@ -2399,7 +2418,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>11</v>
       </c>
@@ -2410,7 +2429,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>2</v>
       </c>
@@ -2421,7 +2440,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>1</v>
       </c>
@@ -2432,7 +2451,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>121</v>
       </c>
@@ -2443,7 +2462,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>12</v>
       </c>
@@ -2454,7 +2473,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>13</v>
       </c>
@@ -2465,7 +2484,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>14</v>
       </c>
@@ -2476,7 +2495,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>15</v>
       </c>
@@ -2487,7 +2506,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>16</v>
       </c>
@@ -2498,7 +2517,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>17</v>
       </c>
@@ -2509,7 +2528,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>18</v>
       </c>
@@ -2520,7 +2539,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>19</v>
       </c>
@@ -2531,7 +2550,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>21</v>
       </c>
@@ -2542,7 +2561,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>20</v>
       </c>
@@ -2553,7 +2572,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>1</v>
       </c>
@@ -2564,7 +2583,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
         <v>22</v>
       </c>
@@ -2575,7 +2594,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
         <v>23</v>
       </c>
@@ -2586,7 +2605,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
         <v>122</v>
       </c>
@@ -2597,7 +2616,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
         <v>24</v>
       </c>
@@ -2608,7 +2627,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
         <v>25</v>
       </c>
@@ -2619,7 +2638,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
         <v>26</v>
       </c>
@@ -2630,7 +2649,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
         <v>123</v>
       </c>
@@ -2641,7 +2660,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
         <v>27</v>
       </c>
@@ -2652,7 +2671,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>124</v>
       </c>
@@ -2663,7 +2682,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>125</v>
       </c>
@@ -2674,7 +2693,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
         <v>126</v>
       </c>
@@ -2685,7 +2704,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
         <v>127</v>
       </c>
@@ -2696,7 +2715,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
         <v>128</v>
       </c>
@@ -2707,7 +2726,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
         <v>28</v>
       </c>
@@ -2718,7 +2737,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>29</v>
       </c>
@@ -2729,7 +2748,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>30</v>
       </c>
@@ -2740,7 +2759,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>31</v>
       </c>
@@ -2751,7 +2770,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
         <v>129</v>
       </c>
@@ -2762,7 +2781,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>32</v>
       </c>
@@ -2773,7 +2792,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
         <v>33</v>
       </c>
@@ -2784,7 +2803,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
         <v>34</v>
       </c>
@@ -2795,7 +2814,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
         <v>130</v>
       </c>
@@ -2806,7 +2825,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>131</v>
       </c>
@@ -2817,7 +2836,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>35</v>
       </c>
@@ -2828,7 +2847,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
         <v>36</v>
       </c>
@@ -2839,7 +2858,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
         <v>37</v>
       </c>
@@ -2850,7 +2869,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
         <v>18</v>
       </c>
@@ -2861,7 +2880,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
         <v>38</v>
       </c>
@@ -2872,7 +2891,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
         <v>132</v>
       </c>
@@ -2883,7 +2902,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>39</v>
       </c>
@@ -2894,7 +2913,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
         <v>133</v>
       </c>
@@ -2905,7 +2924,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
         <v>40</v>
       </c>
@@ -2916,7 +2935,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
         <v>41</v>
       </c>
@@ -2927,7 +2946,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
         <v>42</v>
       </c>
@@ -2938,7 +2957,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
         <v>43</v>
       </c>
@@ -2949,7 +2968,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>46</v>
       </c>
@@ -2960,7 +2979,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
         <v>47</v>
       </c>
@@ -2971,7 +2990,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>45</v>
       </c>
@@ -2982,7 +3001,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
         <v>44</v>
       </c>
@@ -2993,7 +3012,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>1</v>
       </c>
@@ -3004,7 +3023,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
         <v>48</v>
       </c>
@@ -3015,7 +3034,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
         <v>50</v>
       </c>
@@ -3026,7 +3045,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
         <v>51</v>
       </c>
@@ -3037,7 +3056,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
         <v>52</v>
       </c>
@@ -3048,7 +3067,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
         <v>53</v>
       </c>
@@ -3059,7 +3078,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
         <v>54</v>
       </c>
@@ -3070,7 +3089,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
         <v>55</v>
       </c>
@@ -3081,7 +3100,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
         <v>56</v>
       </c>
@@ -3092,7 +3111,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="202" spans="1:3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
         <v>57</v>
       </c>
@@ -3103,7 +3122,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="203" spans="1:3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
         <v>58</v>
       </c>
@@ -3114,7 +3133,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="204" spans="1:3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
         <v>59</v>
       </c>
@@ -3125,7 +3144,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="205" spans="1:3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
         <v>60</v>
       </c>
@@ -3136,7 +3155,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="206" spans="1:3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
         <v>61</v>
       </c>
@@ -3147,7 +3166,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="207" spans="1:3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
         <v>62</v>
       </c>
@@ -3158,7 +3177,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="208" spans="1:3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
         <v>63</v>
       </c>
@@ -3169,7 +3188,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="209" spans="1:3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
         <v>64</v>
       </c>
@@ -3180,7 +3199,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
         <v>65</v>
       </c>
@@ -3191,7 +3210,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="211" spans="1:3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
         <v>66</v>
       </c>
@@ -3202,7 +3221,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="212" spans="1:3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
         <v>67</v>
       </c>
@@ -3213,7 +3232,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
         <v>68</v>
       </c>
@@ -3224,7 +3243,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="6" t="s">
         <v>69</v>
       </c>
@@ -3235,7 +3254,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="6" t="s">
         <v>70</v>
       </c>
@@ -3246,7 +3265,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="216" spans="1:3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="6" t="s">
         <v>134</v>
       </c>
@@ -3257,7 +3276,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
         <v>71</v>
       </c>
@@ -3268,7 +3287,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="6" t="s">
         <v>72</v>
       </c>
@@ -3279,7 +3298,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="6" t="s">
         <v>73</v>
       </c>
@@ -3290,7 +3309,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="6" t="s">
         <v>135</v>
       </c>
@@ -3301,7 +3320,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
         <v>74</v>
       </c>
@@ -3312,7 +3331,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
         <v>75</v>
       </c>
@@ -3323,7 +3342,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
         <v>76</v>
       </c>
@@ -3334,7 +3353,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
         <v>77</v>
       </c>
@@ -3345,7 +3364,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
         <v>78</v>
       </c>
@@ -3356,7 +3375,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="226" spans="1:3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
         <v>136</v>
       </c>
@@ -3367,7 +3386,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="227" spans="1:3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
         <v>80</v>
       </c>
@@ -3378,7 +3397,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
         <v>81</v>
       </c>
@@ -3389,7 +3408,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="229" spans="1:3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
         <v>82</v>
       </c>
@@ -3400,7 +3419,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="230" spans="1:3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
         <v>83</v>
       </c>
@@ -3411,7 +3430,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="231" spans="1:3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
         <v>84</v>
       </c>
@@ -3422,7 +3441,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
         <v>85</v>
       </c>
@@ -3433,7 +3452,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
         <v>79</v>
       </c>
@@ -3444,7 +3463,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
         <v>86</v>
       </c>
@@ -3455,7 +3474,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
         <v>87</v>
       </c>
@@ -3466,7 +3485,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="236" spans="1:3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
         <v>89</v>
       </c>
@@ -3477,7 +3496,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="237" spans="1:3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
         <v>92</v>
       </c>
@@ -3488,7 +3507,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="238" spans="1:3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
         <v>90</v>
       </c>
@@ -3499,7 +3518,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
         <v>93</v>
       </c>
@@ -3510,7 +3529,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="240" spans="1:3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
         <v>95</v>
       </c>
@@ -3521,7 +3540,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
         <v>91</v>
       </c>
@@ -3532,7 +3551,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="242" spans="1:3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
         <v>96</v>
       </c>
@@ -3543,7 +3562,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="243" spans="1:3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
         <v>94</v>
       </c>
@@ -3554,7 +3573,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="244" spans="1:3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="6" t="s">
         <v>88</v>
       </c>
@@ -3565,7 +3584,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="245" spans="1:3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" s="6" t="s">
         <v>97</v>
       </c>
@@ -3576,7 +3595,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="246" spans="1:3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" s="6" t="s">
         <v>49</v>
       </c>
@@ -3587,7 +3606,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" s="6" t="s">
         <v>100</v>
       </c>
@@ -3598,7 +3617,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" s="6" t="s">
         <v>98</v>
       </c>
@@ -3609,7 +3628,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="249" spans="1:3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
         <v>99</v>
       </c>
@@ -3620,7 +3639,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
         <v>44</v>
       </c>
@@ -3631,7 +3650,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="251" spans="1:3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
         <v>101</v>
       </c>
@@ -3642,7 +3661,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="252" spans="1:3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
         <v>102</v>
       </c>
@@ -3653,7 +3672,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>1</v>
       </c>
@@ -3664,7 +3683,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" s="6" t="s">
         <v>104</v>
       </c>
@@ -3675,7 +3694,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
         <v>105</v>
       </c>
@@ -3686,7 +3705,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="256" spans="1:3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
         <v>106</v>
       </c>
@@ -3697,7 +3716,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="257" spans="1:3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
         <v>107</v>
       </c>
@@ -3708,7 +3727,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="258" spans="1:3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
         <v>108</v>
       </c>
@@ -3719,7 +3738,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
         <v>103</v>
       </c>
@@ -3730,7 +3749,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
         <v>47</v>
       </c>
@@ -3741,7 +3760,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
         <v>109</v>
       </c>
@@ -3752,7 +3771,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>1</v>
       </c>
@@ -3763,7 +3782,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
         <v>137</v>
       </c>
@@ -3774,7 +3793,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
         <v>138</v>
       </c>
@@ -3785,7 +3804,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="265" spans="1:3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
         <v>111</v>
       </c>
@@ -3796,7 +3815,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="266" spans="1:3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>1</v>
       </c>
@@ -3807,7 +3826,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="267" spans="1:3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
         <v>115</v>
       </c>
@@ -3818,7 +3837,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
         <v>114</v>
       </c>
@@ -3829,7 +3848,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>1</v>
       </c>
@@ -3840,7 +3859,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="270" spans="1:3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
         <v>113</v>
       </c>
@@ -3851,7 +3870,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="271" spans="1:3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
         <v>110</v>
       </c>
@@ -3862,7 +3881,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="272" spans="1:3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>1</v>
       </c>
@@ -3873,7 +3892,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
         <v>112</v>
       </c>
@@ -3884,7 +3903,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="274" spans="1:3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
         <v>1</v>
       </c>
@@ -3895,7 +3914,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
         <v>117</v>
       </c>
@@ -3906,7 +3925,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
         <v>116</v>
       </c>
@@ -3917,7 +3936,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="277" spans="1:3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
         <v>1</v>
       </c>
@@ -3928,7 +3947,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
         <v>113</v>
       </c>
@@ -3939,7 +3958,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1</v>
       </c>
@@ -3950,7 +3969,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>121</v>
       </c>
@@ -3961,7 +3980,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>12</v>
       </c>
@@ -3972,7 +3991,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>13</v>
       </c>
@@ -3983,7 +4002,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>20</v>
       </c>
@@ -3994,7 +4013,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>21</v>
       </c>
@@ -4005,7 +4024,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>14</v>
       </c>
@@ -4016,7 +4035,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>15</v>
       </c>
@@ -4027,7 +4046,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -4038,7 +4057,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>17</v>
       </c>
@@ -4049,7 +4068,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="289" spans="1:3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>19</v>
       </c>
@@ -4060,7 +4079,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="290" spans="1:3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1</v>
       </c>
@@ -4071,7 +4090,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="291" spans="1:3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>113</v>
       </c>
@@ -4082,7 +4101,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1</v>
       </c>
@@ -4093,7 +4112,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="293" spans="1:3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>111</v>
       </c>
@@ -4104,7 +4123,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="294" spans="1:3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>138</v>
       </c>
@@ -4115,7 +4134,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="295" spans="1:3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>137</v>
       </c>
@@ -4126,7 +4145,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="296" spans="1:3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1</v>
       </c>
@@ -4137,7 +4156,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>2</v>
       </c>
@@ -4148,7 +4167,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>120</v>
       </c>
@@ -4159,7 +4178,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>3</v>
       </c>
@@ -4170,7 +4189,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="300" spans="1:3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>4</v>
       </c>
@@ -4181,7 +4200,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="301" spans="1:3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>5</v>
       </c>
@@ -4192,7 +4211,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>7</v>
       </c>
@@ -4203,7 +4222,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>9</v>
       </c>
@@ -4214,7 +4233,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="304" spans="1:3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>10</v>
       </c>
@@ -4225,7 +4244,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>11</v>
       </c>
@@ -4236,7 +4255,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1</v>
       </c>
@@ -4247,7 +4266,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>112</v>
       </c>
@@ -4258,7 +4277,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="308" spans="1:3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1</v>
       </c>
@@ -4269,7 +4288,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="309" spans="1:3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>87</v>
       </c>
@@ -4280,7 +4299,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="310" spans="1:3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1</v>
       </c>
@@ -4291,7 +4310,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>114</v>
       </c>
@@ -4302,7 +4321,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="312" spans="1:3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1</v>
       </c>
@@ -4313,7 +4332,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="313" spans="1:3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>117</v>
       </c>
@@ -4324,7 +4343,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1</v>
       </c>
@@ -4335,7 +4354,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="315" spans="1:3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>22</v>
       </c>
@@ -4346,7 +4365,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="316" spans="1:3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>23</v>
       </c>
@@ -4357,7 +4376,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="317" spans="1:3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>122</v>
       </c>
@@ -4368,7 +4387,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="318" spans="1:3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>24</v>
       </c>
@@ -4379,7 +4398,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="319" spans="1:3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>25</v>
       </c>
@@ -4390,7 +4409,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="320" spans="1:3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>123</v>
       </c>
@@ -4401,7 +4420,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>27</v>
       </c>
@@ -4412,7 +4431,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>124</v>
       </c>
@@ -4423,7 +4442,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="323" spans="1:3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>125</v>
       </c>
@@ -4434,7 +4453,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>126</v>
       </c>
@@ -4445,7 +4464,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>139</v>
       </c>
@@ -4456,7 +4475,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>128</v>
       </c>
@@ -4467,7 +4486,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>140</v>
       </c>
@@ -4478,7 +4497,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="328" spans="1:3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>129</v>
       </c>
@@ -4489,7 +4508,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="329" spans="1:3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>32</v>
       </c>
@@ -4500,7 +4519,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>34</v>
       </c>
@@ -4511,7 +4530,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="331" spans="1:3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>130</v>
       </c>
@@ -4522,7 +4541,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>131</v>
       </c>
@@ -4533,7 +4552,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="333" spans="1:3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>35</v>
       </c>
@@ -4544,7 +4563,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="334" spans="1:3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>36</v>
       </c>
@@ -4555,7 +4574,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>43</v>
       </c>
@@ -4566,7 +4585,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="336" spans="1:3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>38</v>
       </c>
@@ -4577,7 +4596,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>132</v>
       </c>
@@ -4588,7 +4607,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>39</v>
       </c>
@@ -4599,7 +4618,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>46</v>
       </c>
@@ -4610,7 +4629,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -4621,7 +4640,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>141</v>
       </c>
@@ -4632,7 +4651,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>142</v>
       </c>
@@ -4643,7 +4662,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="343" spans="1:3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>41</v>
       </c>
@@ -4654,7 +4673,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>42</v>
       </c>
@@ -4665,7 +4684,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>18</v>
       </c>
@@ -4676,7 +4695,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>133</v>
       </c>
@@ -4687,7 +4706,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1</v>
       </c>
@@ -4698,7 +4717,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="348" spans="1:3">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>103</v>
       </c>
@@ -4709,7 +4728,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="349" spans="1:3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>109</v>
       </c>
@@ -4720,7 +4739,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>104</v>
       </c>
@@ -4731,7 +4750,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="351" spans="1:3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>47</v>
       </c>
@@ -4742,7 +4761,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>106</v>
       </c>
@@ -4753,7 +4772,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="353" spans="1:3">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>107</v>
       </c>
@@ -4764,7 +4783,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="354" spans="1:3">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>108</v>
       </c>
@@ -4775,7 +4794,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="355" spans="1:3">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1</v>
       </c>
@@ -4786,7 +4805,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="356" spans="1:3">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>86</v>
       </c>
@@ -4797,7 +4816,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="357" spans="1:3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>48</v>
       </c>
@@ -4808,7 +4827,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="358" spans="1:3">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>143</v>
       </c>
@@ -4819,7 +4838,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="359" spans="1:3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>50</v>
       </c>
@@ -4830,7 +4849,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="360" spans="1:3">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>144</v>
       </c>
@@ -4841,7 +4860,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="361" spans="1:3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>51</v>
       </c>
@@ -4852,7 +4871,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="362" spans="1:3">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>52</v>
       </c>
@@ -4863,7 +4882,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="363" spans="1:3">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>53</v>
       </c>
@@ -4874,7 +4893,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="364" spans="1:3">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>145</v>
       </c>
@@ -4885,7 +4904,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="365" spans="1:3">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>146</v>
       </c>
@@ -4896,7 +4915,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="366" spans="1:3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>57</v>
       </c>
@@ -4907,7 +4926,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>92</v>
       </c>
@@ -4918,7 +4937,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="368" spans="1:3">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>59</v>
       </c>
@@ -4929,7 +4948,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="369" spans="1:3">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>60</v>
       </c>
@@ -4940,7 +4959,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="370" spans="1:3">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>62</v>
       </c>
@@ -4951,7 +4970,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="371" spans="1:3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>63</v>
       </c>
@@ -4962,7 +4981,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="372" spans="1:3">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>64</v>
       </c>
@@ -4973,7 +4992,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="373" spans="1:3">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>66</v>
       </c>
@@ -4984,7 +5003,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="374" spans="1:3">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>67</v>
       </c>
@@ -4995,7 +5014,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="375" spans="1:3">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>147</v>
       </c>
@@ -5006,7 +5025,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="376" spans="1:3">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>89</v>
       </c>
@@ -5017,7 +5036,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="377" spans="1:3">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>94</v>
       </c>
@@ -5028,7 +5047,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="378" spans="1:3">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>70</v>
       </c>
@@ -5039,7 +5058,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="379" spans="1:3">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>134</v>
       </c>
@@ -5050,7 +5069,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="380" spans="1:3">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>90</v>
       </c>
@@ -5061,7 +5080,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="381" spans="1:3">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>71</v>
       </c>
@@ -5072,7 +5091,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="382" spans="1:3">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>73</v>
       </c>
@@ -5083,7 +5102,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="383" spans="1:3">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>87</v>
       </c>
@@ -5094,7 +5113,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="384" spans="1:3">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>135</v>
       </c>
@@ -5105,7 +5124,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="385" spans="1:3">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>74</v>
       </c>
@@ -5116,7 +5135,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="386" spans="1:3">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>76</v>
       </c>
@@ -5127,7 +5146,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="387" spans="1:3">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>148</v>
       </c>
@@ -5138,7 +5157,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="388" spans="1:3">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>98</v>
       </c>
@@ -5149,7 +5168,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="389" spans="1:3">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>99</v>
       </c>
@@ -5160,7 +5179,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="390" spans="1:3">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>149</v>
       </c>
@@ -5171,7 +5190,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="391" spans="1:3">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>102</v>
       </c>
@@ -5182,7 +5201,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="392" spans="1:3">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>79</v>
       </c>
@@ -5193,7 +5212,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="393" spans="1:3">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>150</v>
       </c>
@@ -5204,7 +5223,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="394" spans="1:3">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>136</v>
       </c>
@@ -5215,7 +5234,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="395" spans="1:3">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>82</v>
       </c>
@@ -5226,7 +5245,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="396" spans="1:3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>83</v>
       </c>
@@ -5237,7 +5256,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="397" spans="1:3">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>88</v>
       </c>
@@ -5248,7 +5267,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="398" spans="1:3">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>93</v>
       </c>
@@ -5259,7 +5278,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="399" spans="1:3">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>95</v>
       </c>
@@ -5270,7 +5289,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="400" spans="1:3">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>96</v>
       </c>
@@ -5281,7 +5300,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="401" spans="1:3">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>151</v>
       </c>
@@ -5292,7 +5311,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="402" spans="1:3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>97</v>
       </c>
@@ -5303,7 +5322,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>44</v>
       </c>
@@ -5314,7 +5333,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="404" spans="1:3">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>85</v>
       </c>
@@ -5325,7 +5344,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>100</v>
       </c>
@@ -5336,7 +5355,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="406" spans="1:3">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>69</v>
       </c>
@@ -5347,7 +5366,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="407" spans="1:3">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>49</v>
       </c>
@@ -5358,7 +5377,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="408" spans="1:3">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>84</v>
       </c>
@@ -5369,12 +5388,1379 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="409" spans="1:3">
-      <c r="B409" s="9">
-        <v>0.99435518888406427</v>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A409" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B409" s="5">
+        <v>1</v>
       </c>
       <c r="C409" s="8">
-        <v>46082</v>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B410" s="4">
+        <v>0.96464646464646464</v>
+      </c>
+      <c r="C410" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B411" s="5">
+        <v>1</v>
+      </c>
+      <c r="C411" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B412" s="5">
+        <v>1</v>
+      </c>
+      <c r="C412" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B413" s="5">
+        <v>1</v>
+      </c>
+      <c r="C413" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B414" s="5">
+        <v>1</v>
+      </c>
+      <c r="C414" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B415" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="C415" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B416" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C416" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B417" s="5">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="C417" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B418" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C418" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B419" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C419" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B420" s="4">
+        <v>0.93243243243243246</v>
+      </c>
+      <c r="C420" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B421" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C421" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A422" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B422" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C422" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A423" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B423" s="5">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C423" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A424" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B424" s="5">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C424" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B425" s="5">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C425" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B426" s="5">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C426" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B427" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C427" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B428" s="5">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="C428" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B429" s="5">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="C429" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B430" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="C430" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A431" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B431" s="5">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="C431" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A432" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B432" s="4">
+        <v>0.93097643097643101</v>
+      </c>
+      <c r="C432" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A433" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B433" s="5">
+        <v>1</v>
+      </c>
+      <c r="C433" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A434" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B434" s="5">
+        <v>1</v>
+      </c>
+      <c r="C434" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A435" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B435" s="5">
+        <v>1</v>
+      </c>
+      <c r="C435" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A436" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B436" s="5">
+        <v>1</v>
+      </c>
+      <c r="C436" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A437" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B437" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="C437" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A438" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B438" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C438" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A439" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B439" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C439" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A440" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B440" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C440" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A441" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B441" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C441" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A442" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B442" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C442" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A443" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B443" s="5">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="C443" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A444" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B444" s="5">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="C444" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A445" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B445" s="5">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="C445" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A446" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B446" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C446" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A447" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B447" s="5">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="C447" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A448" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B448" s="5">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="C448" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A449" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B449" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="C449" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A450" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B450" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="C450" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A451" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B451" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="C451" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A452" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B452" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C452" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A453" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B453" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C453" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A454" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B454" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="C454" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A455" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B455" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="C455" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A456" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B456" s="5">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="C456" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A457" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B457" s="5">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="C457" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A458" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B458" s="5">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="C458" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A459" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B459" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="C459" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A460" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B460" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C460" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A461" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B461" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C461" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A462" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B462" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="C462" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A463" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B463" s="4">
+        <v>0.9242424242424242</v>
+      </c>
+      <c r="C463" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A464" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B464" s="5">
+        <v>1</v>
+      </c>
+      <c r="C464" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A465" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B465" s="5">
+        <v>1</v>
+      </c>
+      <c r="C465" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A466" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B466" s="5">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C466" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A467" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B467" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="C467" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A468" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B468" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="C468" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A469" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B469" s="5">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="C469" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A470" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B470" s="5">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="C470" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A471" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B471" s="4">
+        <v>0.92230070635721495</v>
+      </c>
+      <c r="C471" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A472" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B472" s="5">
+        <v>1</v>
+      </c>
+      <c r="C472" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A473" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B473" s="5">
+        <v>1</v>
+      </c>
+      <c r="C473" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A474" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B474" s="5">
+        <v>1</v>
+      </c>
+      <c r="C474" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B475" s="5">
+        <v>1</v>
+      </c>
+      <c r="C475" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A476" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B476" s="5">
+        <v>1</v>
+      </c>
+      <c r="C476" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A477" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B477" s="5">
+        <v>1</v>
+      </c>
+      <c r="C477" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A478" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B478" s="5">
+        <v>1</v>
+      </c>
+      <c r="C478" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A479" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B479" s="5">
+        <v>1</v>
+      </c>
+      <c r="C479" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B480" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C480" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A481" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B481" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C481" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A482" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B482" s="5">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="C482" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A483" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B483" s="5">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="C483" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B484" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C484" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A485" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B485" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C485" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A486" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B486" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C486" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A487" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B487" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C487" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B488" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C488" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A489" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B489" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C489" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A490" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B490" s="5">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C490" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A491" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B491" s="5">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C491" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A492" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B492" s="5">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C492" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A493" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B493" s="5">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="C493" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B494" s="5">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="C494" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B495" s="5">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="C495" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A496" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B496" s="5">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="C496" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A497" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B497" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="C497" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A498" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B498" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C498" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B499" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C499" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A500" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B500" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C500" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A501" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B501" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C501" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A502" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B502" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C502" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B503" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C503" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A504" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B504" s="5">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C504" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A505" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B505" s="5">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="C505" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A506" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B506" s="5">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="C506" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A507" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B507" s="5">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="C507" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A508" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B508" s="5">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="C508" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A509" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B509" s="5">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="C509" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A510" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B510" s="5">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="C510" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A511" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B511" s="5">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="C511" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A512" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B512" s="5">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="C512" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A513" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B513" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="C513" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A514" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B514" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="C514" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A515" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B515" s="5">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="C515" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A516" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B516" s="5">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="C516" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A517" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B517" s="5">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="C517" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A518" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B518" s="5">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="C518" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A519" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B519" s="5">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="C519" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A520" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B520" s="5">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="C520" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A521" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B521" s="5">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="C521" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A522" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B522" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="C522" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A523" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B523" s="5">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="C523" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A524" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B524" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C524" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A525" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B525" s="5">
+        <v>1</v>
+      </c>
+      <c r="C525" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A526" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B526" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="C526" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A527" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B527" s="5">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="C527" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A528" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B528" s="4">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="C528" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A529" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B529" s="5">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="C529" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B530" s="4">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="C530" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B531" s="5">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="C531" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B532" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C532" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B533" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C533" s="8">
+        <v>46113</v>
       </c>
     </row>
   </sheetData>

--- a/data/JLL.xlsx
+++ b/data/JLL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG armazem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6239B33-19D9-4A7B-A5B9-12386268B7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8960061B-3CD9-4E47-8B7B-7570FBD469D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JLL" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="185">
   <si>
     <t>% Cumprimento de Jornada</t>
   </si>
@@ -507,13 +507,94 @@
   </si>
   <si>
     <t>JOAO MARIA MESTRIA</t>
+  </si>
+  <si>
+    <t>EDUARDA MARIA ARTAO LOVATO</t>
+  </si>
+  <si>
+    <t>ADRIANA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ANTONIO IZIDIO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>DIONES RODRIGUES DE SA</t>
+  </si>
+  <si>
+    <t>EDUARDO GUTIERREZ FREIRES</t>
+  </si>
+  <si>
+    <t>ELIAS NATA OLIVEIRA CORREIA</t>
+  </si>
+  <si>
+    <t>ENDRICK VINICIUS COSTA PINTO</t>
+  </si>
+  <si>
+    <t>FELIPE SANTOS CARNEIRO</t>
+  </si>
+  <si>
+    <t>GABRIEL KACHUTSKI TAMELIN</t>
+  </si>
+  <si>
+    <t>GUILHERME INGLES FERREIRA</t>
+  </si>
+  <si>
+    <t>ISABELA ADRIANA FERREIRA DE LIMA</t>
+  </si>
+  <si>
+    <t>KELVIN GUSTAVO MUJICA ORDAZ</t>
+  </si>
+  <si>
+    <t>MATEUS PIETROBELLI RIBEIRO GOMES</t>
+  </si>
+  <si>
+    <t>PABLO VITOR CORREIA</t>
+  </si>
+  <si>
+    <t>RUBEN CESAR SILVA DE SOUZA</t>
+  </si>
+  <si>
+    <t>SILVIO BRUNO BORGES ROSA</t>
+  </si>
+  <si>
+    <t>ADRIAN SAMUEL FERREIRA</t>
+  </si>
+  <si>
+    <t>ADRIANO JOSE DE LIMA</t>
+  </si>
+  <si>
+    <t>BRUNO DE LIMA SANTOS</t>
+  </si>
+  <si>
+    <t>GILMAR DE CASTRO</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO BARBOSA MOURA</t>
+  </si>
+  <si>
+    <t>NYCOLAS DA LUZ E SILVA</t>
+  </si>
+  <si>
+    <t>RODRIGO ROSA</t>
+  </si>
+  <si>
+    <t>TAYLOR ZACK DA SILVA DE QUEIROZ</t>
+  </si>
+  <si>
+    <t>Valdemir Gabriel Monteiro</t>
+  </si>
+  <si>
+    <t>WELLINGTON GABRIEL TEIXEIRA PINTO</t>
+  </si>
+  <si>
+    <t>WESLEY EDUARDO MATHIAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -569,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -580,6 +661,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -894,15 +979,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C533"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C668"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="5" width="27.109375" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="5" width="27.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>118</v>
       </c>
@@ -913,7 +998,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="6"/>
       <c r="B2" s="4">
         <v>0.89977528089887637</v>
@@ -922,7 +1007,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -933,7 +1018,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -944,7 +1029,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -955,7 +1040,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -966,7 +1051,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -977,7 +1062,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -988,7 +1073,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -999,7 +1084,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1010,7 +1095,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1021,7 +1106,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1032,7 +1117,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1043,7 +1128,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
@@ -1054,7 +1139,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -1065,7 +1150,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
@@ -1076,7 +1161,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -1087,7 +1172,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -1098,7 +1183,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -1109,7 +1194,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -1120,7 +1205,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -1131,7 +1216,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -1142,7 +1227,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -1153,7 +1238,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
@@ -1164,7 +1249,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
         <v>1</v>
       </c>
@@ -1175,7 +1260,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
@@ -1186,7 +1271,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
         <v>23</v>
       </c>
@@ -1197,7 +1282,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -1208,7 +1293,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>25</v>
       </c>
@@ -1219,7 +1304,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
@@ -1230,7 +1315,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
@@ -1241,7 +1326,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
@@ -1252,7 +1337,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -1263,7 +1348,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
@@ -1274,7 +1359,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
@@ -1285,7 +1370,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -1296,7 +1381,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
         <v>33</v>
       </c>
@@ -1307,7 +1392,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
@@ -1318,7 +1403,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
         <v>35</v>
       </c>
@@ -1329,7 +1414,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
@@ -1340,7 +1425,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
         <v>37</v>
       </c>
@@ -1351,7 +1436,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
         <v>38</v>
       </c>
@@ -1362,7 +1447,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
@@ -1373,7 +1458,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
         <v>40</v>
       </c>
@@ -1384,7 +1469,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
         <v>41</v>
       </c>
@@ -1395,7 +1480,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
         <v>42</v>
       </c>
@@ -1406,7 +1491,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
@@ -1417,7 +1502,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
         <v>44</v>
       </c>
@@ -1428,7 +1513,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
         <v>45</v>
       </c>
@@ -1439,7 +1524,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
         <v>46</v>
       </c>
@@ -1450,7 +1535,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
         <v>47</v>
       </c>
@@ -1461,7 +1546,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" s="3" t="s">
         <v>1</v>
       </c>
@@ -1472,7 +1557,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
         <v>48</v>
       </c>
@@ -1483,7 +1568,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
         <v>49</v>
       </c>
@@ -1494,7 +1579,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
         <v>50</v>
       </c>
@@ -1505,7 +1590,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56" s="2" t="s">
         <v>51</v>
       </c>
@@ -1516,7 +1601,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57" s="2" t="s">
         <v>52</v>
       </c>
@@ -1527,7 +1612,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
         <v>53</v>
       </c>
@@ -1538,7 +1623,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" s="2" t="s">
         <v>54</v>
       </c>
@@ -1549,7 +1634,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3">
       <c r="A60" s="2" t="s">
         <v>55</v>
       </c>
@@ -1560,7 +1645,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" s="2" t="s">
         <v>56</v>
       </c>
@@ -1571,7 +1656,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62" s="2" t="s">
         <v>57</v>
       </c>
@@ -1582,7 +1667,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63" s="2" t="s">
         <v>58</v>
       </c>
@@ -1593,7 +1678,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64" s="2" t="s">
         <v>59</v>
       </c>
@@ -1604,7 +1689,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" s="2" t="s">
         <v>60</v>
       </c>
@@ -1615,7 +1700,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" s="2" t="s">
         <v>61</v>
       </c>
@@ -1626,7 +1711,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" s="2" t="s">
         <v>62</v>
       </c>
@@ -1637,7 +1722,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3">
       <c r="A68" s="2" t="s">
         <v>63</v>
       </c>
@@ -1648,7 +1733,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" s="2" t="s">
         <v>64</v>
       </c>
@@ -1659,7 +1744,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" s="2" t="s">
         <v>65</v>
       </c>
@@ -1670,7 +1755,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
         <v>66</v>
       </c>
@@ -1681,7 +1766,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
         <v>67</v>
       </c>
@@ -1692,7 +1777,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
         <v>68</v>
       </c>
@@ -1703,7 +1788,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="A74" s="2" t="s">
         <v>69</v>
       </c>
@@ -1714,7 +1799,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
         <v>70</v>
       </c>
@@ -1725,7 +1810,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
         <v>71</v>
       </c>
@@ -1736,7 +1821,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
         <v>72</v>
       </c>
@@ -1747,7 +1832,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
         <v>73</v>
       </c>
@@ -1758,7 +1843,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
         <v>74</v>
       </c>
@@ -1769,7 +1854,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3">
       <c r="A80" s="2" t="s">
         <v>75</v>
       </c>
@@ -1780,7 +1865,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
         <v>76</v>
       </c>
@@ -1791,7 +1876,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
         <v>77</v>
       </c>
@@ -1802,7 +1887,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3">
       <c r="A83" s="2" t="s">
         <v>78</v>
       </c>
@@ -1813,7 +1898,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
         <v>79</v>
       </c>
@@ -1824,7 +1909,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
         <v>80</v>
       </c>
@@ -1835,7 +1920,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
         <v>81</v>
       </c>
@@ -1846,7 +1931,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
         <v>82</v>
       </c>
@@ -1857,7 +1942,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
         <v>83</v>
       </c>
@@ -1868,7 +1953,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
         <v>84</v>
       </c>
@@ -1879,7 +1964,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
         <v>85</v>
       </c>
@@ -1890,7 +1975,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
         <v>86</v>
       </c>
@@ -1901,7 +1986,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3">
       <c r="A92" s="2" t="s">
         <v>87</v>
       </c>
@@ -1912,7 +1997,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
         <v>88</v>
       </c>
@@ -1923,7 +2008,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
         <v>89</v>
       </c>
@@ -1934,7 +2019,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
         <v>90</v>
       </c>
@@ -1945,7 +2030,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
         <v>91</v>
       </c>
@@ -1956,7 +2041,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3">
       <c r="A97" s="2" t="s">
         <v>92</v>
       </c>
@@ -1967,7 +2052,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3">
       <c r="A98" s="2" t="s">
         <v>93</v>
       </c>
@@ -1978,7 +2063,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3">
       <c r="A99" s="2" t="s">
         <v>94</v>
       </c>
@@ -1989,7 +2074,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3">
       <c r="A100" s="2" t="s">
         <v>95</v>
       </c>
@@ -2000,7 +2085,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3">
       <c r="A101" s="2" t="s">
         <v>96</v>
       </c>
@@ -2011,7 +2096,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3">
       <c r="A102" s="2" t="s">
         <v>97</v>
       </c>
@@ -2022,7 +2107,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3">
       <c r="A103" s="2" t="s">
         <v>98</v>
       </c>
@@ -2033,7 +2118,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3">
       <c r="A104" s="2" t="s">
         <v>99</v>
       </c>
@@ -2044,7 +2129,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3">
       <c r="A105" s="2" t="s">
         <v>100</v>
       </c>
@@ -2055,7 +2140,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3">
       <c r="A106" s="2" t="s">
         <v>101</v>
       </c>
@@ -2066,7 +2151,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3">
       <c r="A107" s="2" t="s">
         <v>102</v>
       </c>
@@ -2077,7 +2162,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3">
       <c r="A108" s="3" t="s">
         <v>1</v>
       </c>
@@ -2088,7 +2173,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3">
       <c r="A109" s="2" t="s">
         <v>103</v>
       </c>
@@ -2099,7 +2184,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3">
       <c r="A110" s="2" t="s">
         <v>104</v>
       </c>
@@ -2110,7 +2195,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3">
       <c r="A111" s="2" t="s">
         <v>105</v>
       </c>
@@ -2121,7 +2206,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3">
       <c r="A112" s="2" t="s">
         <v>106</v>
       </c>
@@ -2132,7 +2217,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3">
       <c r="A113" s="2" t="s">
         <v>107</v>
       </c>
@@ -2143,7 +2228,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3">
       <c r="A114" s="2" t="s">
         <v>108</v>
       </c>
@@ -2154,7 +2239,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3">
       <c r="A115" s="2" t="s">
         <v>109</v>
       </c>
@@ -2165,7 +2250,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3">
       <c r="A116" s="3" t="s">
         <v>1</v>
       </c>
@@ -2176,7 +2261,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3">
       <c r="A117" s="2" t="s">
         <v>110</v>
       </c>
@@ -2187,7 +2272,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3">
       <c r="A118" s="3" t="s">
         <v>1</v>
       </c>
@@ -2198,7 +2283,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3">
       <c r="A119" s="2" t="s">
         <v>111</v>
       </c>
@@ -2209,7 +2294,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3">
       <c r="A120" s="3" t="s">
         <v>1</v>
       </c>
@@ -2220,7 +2305,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3">
       <c r="A121" s="2" t="s">
         <v>112</v>
       </c>
@@ -2231,7 +2316,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3">
       <c r="A122" s="3" t="s">
         <v>1</v>
       </c>
@@ -2242,7 +2327,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3">
       <c r="A123" s="2" t="s">
         <v>113</v>
       </c>
@@ -2253,7 +2338,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3">
       <c r="A124" s="3" t="s">
         <v>1</v>
       </c>
@@ -2264,7 +2349,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3">
       <c r="A125" s="2" t="s">
         <v>114</v>
       </c>
@@ -2275,7 +2360,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3">
       <c r="A126" s="2" t="s">
         <v>115</v>
       </c>
@@ -2286,7 +2371,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3">
       <c r="A127" s="3" t="s">
         <v>1</v>
       </c>
@@ -2297,7 +2382,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3">
       <c r="A128" s="2" t="s">
         <v>116</v>
       </c>
@@ -2308,7 +2393,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3">
       <c r="A129" s="2" t="s">
         <v>117</v>
       </c>
@@ -2319,7 +2404,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3">
       <c r="A130" s="6" t="s">
         <v>120</v>
       </c>
@@ -2330,7 +2415,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3">
       <c r="A131" s="6" t="s">
         <v>3</v>
       </c>
@@ -2341,7 +2426,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3">
       <c r="A132" s="6" t="s">
         <v>4</v>
       </c>
@@ -2352,7 +2437,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3">
       <c r="A133" s="6" t="s">
         <v>5</v>
       </c>
@@ -2363,7 +2448,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3">
       <c r="A134" s="6" t="s">
         <v>6</v>
       </c>
@@ -2374,7 +2459,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3">
       <c r="A135" s="6" t="s">
         <v>7</v>
       </c>
@@ -2385,7 +2470,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3">
       <c r="A136" s="6" t="s">
         <v>8</v>
       </c>
@@ -2396,7 +2481,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3">
       <c r="A137" s="6" t="s">
         <v>9</v>
       </c>
@@ -2407,7 +2492,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3">
       <c r="A138" s="6" t="s">
         <v>10</v>
       </c>
@@ -2418,7 +2503,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3">
       <c r="A139" s="6" t="s">
         <v>11</v>
       </c>
@@ -2429,7 +2514,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3">
       <c r="A140" s="6" t="s">
         <v>2</v>
       </c>
@@ -2440,7 +2525,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3">
       <c r="A141" s="3" t="s">
         <v>1</v>
       </c>
@@ -2451,7 +2536,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3">
       <c r="A142" s="6" t="s">
         <v>121</v>
       </c>
@@ -2462,7 +2547,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3">
       <c r="A143" s="6" t="s">
         <v>12</v>
       </c>
@@ -2473,7 +2558,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3">
       <c r="A144" s="6" t="s">
         <v>13</v>
       </c>
@@ -2484,7 +2569,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3">
       <c r="A145" s="6" t="s">
         <v>14</v>
       </c>
@@ -2495,7 +2580,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3">
       <c r="A146" s="6" t="s">
         <v>15</v>
       </c>
@@ -2506,7 +2591,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3">
       <c r="A147" s="6" t="s">
         <v>16</v>
       </c>
@@ -2517,7 +2602,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3">
       <c r="A148" s="6" t="s">
         <v>17</v>
       </c>
@@ -2528,7 +2613,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3">
       <c r="A149" s="6" t="s">
         <v>18</v>
       </c>
@@ -2539,7 +2624,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3">
       <c r="A150" s="6" t="s">
         <v>19</v>
       </c>
@@ -2550,7 +2635,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3">
       <c r="A151" s="6" t="s">
         <v>21</v>
       </c>
@@ -2561,7 +2646,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3">
       <c r="A152" s="6" t="s">
         <v>20</v>
       </c>
@@ -2572,7 +2657,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3">
       <c r="A153" s="3" t="s">
         <v>1</v>
       </c>
@@ -2583,7 +2668,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3">
       <c r="A154" s="6" t="s">
         <v>22</v>
       </c>
@@ -2594,7 +2679,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3">
       <c r="A155" s="6" t="s">
         <v>23</v>
       </c>
@@ -2605,7 +2690,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3">
       <c r="A156" s="6" t="s">
         <v>122</v>
       </c>
@@ -2616,7 +2701,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3">
       <c r="A157" s="6" t="s">
         <v>24</v>
       </c>
@@ -2627,7 +2712,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3">
       <c r="A158" s="6" t="s">
         <v>25</v>
       </c>
@@ -2638,7 +2723,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3">
       <c r="A159" s="6" t="s">
         <v>26</v>
       </c>
@@ -2649,7 +2734,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3">
       <c r="A160" s="6" t="s">
         <v>123</v>
       </c>
@@ -2660,7 +2745,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3">
       <c r="A161" s="6" t="s">
         <v>27</v>
       </c>
@@ -2671,7 +2756,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3">
       <c r="A162" s="6" t="s">
         <v>124</v>
       </c>
@@ -2682,7 +2767,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3">
       <c r="A163" s="6" t="s">
         <v>125</v>
       </c>
@@ -2693,7 +2778,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3">
       <c r="A164" s="6" t="s">
         <v>126</v>
       </c>
@@ -2704,7 +2789,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3">
       <c r="A165" s="6" t="s">
         <v>127</v>
       </c>
@@ -2715,7 +2800,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3">
       <c r="A166" s="6" t="s">
         <v>128</v>
       </c>
@@ -2726,7 +2811,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3">
       <c r="A167" s="6" t="s">
         <v>28</v>
       </c>
@@ -2737,7 +2822,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3">
       <c r="A168" s="6" t="s">
         <v>29</v>
       </c>
@@ -2748,7 +2833,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3">
       <c r="A169" s="6" t="s">
         <v>30</v>
       </c>
@@ -2759,7 +2844,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3">
       <c r="A170" s="6" t="s">
         <v>31</v>
       </c>
@@ -2770,7 +2855,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3">
       <c r="A171" s="6" t="s">
         <v>129</v>
       </c>
@@ -2781,7 +2866,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3">
       <c r="A172" s="6" t="s">
         <v>32</v>
       </c>
@@ -2792,7 +2877,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3">
       <c r="A173" s="6" t="s">
         <v>33</v>
       </c>
@@ -2803,7 +2888,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3">
       <c r="A174" s="6" t="s">
         <v>34</v>
       </c>
@@ -2814,7 +2899,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3">
       <c r="A175" s="6" t="s">
         <v>130</v>
       </c>
@@ -2825,7 +2910,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3">
       <c r="A176" s="6" t="s">
         <v>131</v>
       </c>
@@ -2836,7 +2921,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3">
       <c r="A177" s="6" t="s">
         <v>35</v>
       </c>
@@ -2847,7 +2932,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3">
       <c r="A178" s="6" t="s">
         <v>36</v>
       </c>
@@ -2858,7 +2943,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3">
       <c r="A179" s="6" t="s">
         <v>37</v>
       </c>
@@ -2869,7 +2954,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3">
       <c r="A180" s="6" t="s">
         <v>18</v>
       </c>
@@ -2880,7 +2965,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3">
       <c r="A181" s="6" t="s">
         <v>38</v>
       </c>
@@ -2891,7 +2976,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3">
       <c r="A182" s="6" t="s">
         <v>132</v>
       </c>
@@ -2902,7 +2987,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3">
       <c r="A183" s="6" t="s">
         <v>39</v>
       </c>
@@ -2913,7 +2998,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3">
       <c r="A184" s="6" t="s">
         <v>133</v>
       </c>
@@ -2924,7 +3009,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3">
       <c r="A185" s="6" t="s">
         <v>40</v>
       </c>
@@ -2935,7 +3020,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3">
       <c r="A186" s="6" t="s">
         <v>41</v>
       </c>
@@ -2946,7 +3031,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3">
       <c r="A187" s="6" t="s">
         <v>42</v>
       </c>
@@ -2957,7 +3042,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3">
       <c r="A188" s="6" t="s">
         <v>43</v>
       </c>
@@ -2968,7 +3053,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3">
       <c r="A189" s="6" t="s">
         <v>46</v>
       </c>
@@ -2979,7 +3064,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3">
       <c r="A190" s="6" t="s">
         <v>47</v>
       </c>
@@ -2990,7 +3075,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3">
       <c r="A191" s="6" t="s">
         <v>45</v>
       </c>
@@ -3001,7 +3086,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3">
       <c r="A192" s="6" t="s">
         <v>44</v>
       </c>
@@ -3012,7 +3097,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3">
       <c r="A193" s="3" t="s">
         <v>1</v>
       </c>
@@ -3023,7 +3108,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3">
       <c r="A194" s="6" t="s">
         <v>48</v>
       </c>
@@ -3034,7 +3119,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3">
       <c r="A195" s="6" t="s">
         <v>50</v>
       </c>
@@ -3045,7 +3130,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3">
       <c r="A196" s="6" t="s">
         <v>51</v>
       </c>
@@ -3056,7 +3141,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3">
       <c r="A197" s="6" t="s">
         <v>52</v>
       </c>
@@ -3067,7 +3152,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3">
       <c r="A198" s="6" t="s">
         <v>53</v>
       </c>
@@ -3078,7 +3163,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3">
       <c r="A199" s="6" t="s">
         <v>54</v>
       </c>
@@ -3089,7 +3174,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3">
       <c r="A200" s="6" t="s">
         <v>55</v>
       </c>
@@ -3100,7 +3185,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3">
       <c r="A201" s="6" t="s">
         <v>56</v>
       </c>
@@ -3111,7 +3196,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3">
       <c r="A202" s="6" t="s">
         <v>57</v>
       </c>
@@ -3122,7 +3207,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3">
       <c r="A203" s="6" t="s">
         <v>58</v>
       </c>
@@ -3133,7 +3218,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3">
       <c r="A204" s="6" t="s">
         <v>59</v>
       </c>
@@ -3144,7 +3229,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3">
       <c r="A205" s="6" t="s">
         <v>60</v>
       </c>
@@ -3155,7 +3240,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3">
       <c r="A206" s="6" t="s">
         <v>61</v>
       </c>
@@ -3166,7 +3251,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3">
       <c r="A207" s="6" t="s">
         <v>62</v>
       </c>
@@ -3177,7 +3262,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3">
       <c r="A208" s="6" t="s">
         <v>63</v>
       </c>
@@ -3188,7 +3273,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3">
       <c r="A209" s="6" t="s">
         <v>64</v>
       </c>
@@ -3199,7 +3284,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3">
       <c r="A210" s="6" t="s">
         <v>65</v>
       </c>
@@ -3210,7 +3295,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3">
       <c r="A211" s="6" t="s">
         <v>66</v>
       </c>
@@ -3221,7 +3306,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3">
       <c r="A212" s="6" t="s">
         <v>67</v>
       </c>
@@ -3232,7 +3317,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3">
       <c r="A213" s="6" t="s">
         <v>68</v>
       </c>
@@ -3243,7 +3328,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3">
       <c r="A214" s="6" t="s">
         <v>69</v>
       </c>
@@ -3254,7 +3339,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3">
       <c r="A215" s="6" t="s">
         <v>70</v>
       </c>
@@ -3265,7 +3350,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3">
       <c r="A216" s="6" t="s">
         <v>134</v>
       </c>
@@ -3276,7 +3361,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3">
       <c r="A217" s="6" t="s">
         <v>71</v>
       </c>
@@ -3287,7 +3372,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3">
       <c r="A218" s="6" t="s">
         <v>72</v>
       </c>
@@ -3298,7 +3383,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3">
       <c r="A219" s="6" t="s">
         <v>73</v>
       </c>
@@ -3309,7 +3394,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3">
       <c r="A220" s="6" t="s">
         <v>135</v>
       </c>
@@ -3320,7 +3405,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3">
       <c r="A221" s="6" t="s">
         <v>74</v>
       </c>
@@ -3331,7 +3416,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3">
       <c r="A222" s="6" t="s">
         <v>75</v>
       </c>
@@ -3342,7 +3427,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3">
       <c r="A223" s="6" t="s">
         <v>76</v>
       </c>
@@ -3353,7 +3438,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3">
       <c r="A224" s="6" t="s">
         <v>77</v>
       </c>
@@ -3364,7 +3449,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3">
       <c r="A225" s="6" t="s">
         <v>78</v>
       </c>
@@ -3375,7 +3460,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3">
       <c r="A226" s="6" t="s">
         <v>136</v>
       </c>
@@ -3386,7 +3471,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3">
       <c r="A227" s="6" t="s">
         <v>80</v>
       </c>
@@ -3397,7 +3482,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3">
       <c r="A228" s="6" t="s">
         <v>81</v>
       </c>
@@ -3408,7 +3493,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3">
       <c r="A229" s="6" t="s">
         <v>82</v>
       </c>
@@ -3419,7 +3504,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3">
       <c r="A230" s="6" t="s">
         <v>83</v>
       </c>
@@ -3430,7 +3515,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3">
       <c r="A231" s="6" t="s">
         <v>84</v>
       </c>
@@ -3441,7 +3526,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3">
       <c r="A232" s="6" t="s">
         <v>85</v>
       </c>
@@ -3452,7 +3537,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3">
       <c r="A233" s="6" t="s">
         <v>79</v>
       </c>
@@ -3463,7 +3548,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3">
       <c r="A234" s="6" t="s">
         <v>86</v>
       </c>
@@ -3474,7 +3559,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3">
       <c r="A235" s="6" t="s">
         <v>87</v>
       </c>
@@ -3485,7 +3570,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3">
       <c r="A236" s="6" t="s">
         <v>89</v>
       </c>
@@ -3496,7 +3581,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3">
       <c r="A237" s="6" t="s">
         <v>92</v>
       </c>
@@ -3507,7 +3592,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3">
       <c r="A238" s="6" t="s">
         <v>90</v>
       </c>
@@ -3518,7 +3603,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3">
       <c r="A239" s="6" t="s">
         <v>93</v>
       </c>
@@ -3529,7 +3614,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3">
       <c r="A240" s="6" t="s">
         <v>95</v>
       </c>
@@ -3540,7 +3625,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3">
       <c r="A241" s="6" t="s">
         <v>91</v>
       </c>
@@ -3551,7 +3636,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3">
       <c r="A242" s="6" t="s">
         <v>96</v>
       </c>
@@ -3562,7 +3647,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3">
       <c r="A243" s="6" t="s">
         <v>94</v>
       </c>
@@ -3573,7 +3658,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3">
       <c r="A244" s="6" t="s">
         <v>88</v>
       </c>
@@ -3584,7 +3669,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3">
       <c r="A245" s="6" t="s">
         <v>97</v>
       </c>
@@ -3595,7 +3680,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3">
       <c r="A246" s="6" t="s">
         <v>49</v>
       </c>
@@ -3606,7 +3691,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3">
       <c r="A247" s="6" t="s">
         <v>100</v>
       </c>
@@ -3617,7 +3702,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3">
       <c r="A248" s="6" t="s">
         <v>98</v>
       </c>
@@ -3628,7 +3713,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3">
       <c r="A249" s="6" t="s">
         <v>99</v>
       </c>
@@ -3639,7 +3724,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3">
       <c r="A250" s="6" t="s">
         <v>44</v>
       </c>
@@ -3650,7 +3735,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3">
       <c r="A251" s="6" t="s">
         <v>101</v>
       </c>
@@ -3661,7 +3746,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3">
       <c r="A252" s="6" t="s">
         <v>102</v>
       </c>
@@ -3672,7 +3757,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3">
       <c r="A253" s="3" t="s">
         <v>1</v>
       </c>
@@ -3683,7 +3768,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3">
       <c r="A254" s="6" t="s">
         <v>104</v>
       </c>
@@ -3694,7 +3779,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3">
       <c r="A255" s="6" t="s">
         <v>105</v>
       </c>
@@ -3705,7 +3790,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3">
       <c r="A256" s="6" t="s">
         <v>106</v>
       </c>
@@ -3716,7 +3801,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3">
       <c r="A257" s="6" t="s">
         <v>107</v>
       </c>
@@ -3727,7 +3812,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3">
       <c r="A258" s="6" t="s">
         <v>108</v>
       </c>
@@ -3738,7 +3823,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3">
       <c r="A259" s="6" t="s">
         <v>103</v>
       </c>
@@ -3749,7 +3834,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3">
       <c r="A260" s="6" t="s">
         <v>47</v>
       </c>
@@ -3760,7 +3845,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3">
       <c r="A261" s="6" t="s">
         <v>109</v>
       </c>
@@ -3771,7 +3856,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3">
       <c r="A262" s="3" t="s">
         <v>1</v>
       </c>
@@ -3782,7 +3867,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3">
       <c r="A263" s="6" t="s">
         <v>137</v>
       </c>
@@ -3793,7 +3878,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3">
       <c r="A264" s="6" t="s">
         <v>138</v>
       </c>
@@ -3804,7 +3889,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3">
       <c r="A265" s="6" t="s">
         <v>111</v>
       </c>
@@ -3815,7 +3900,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3">
       <c r="A266" s="3" t="s">
         <v>1</v>
       </c>
@@ -3826,7 +3911,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3">
       <c r="A267" s="6" t="s">
         <v>115</v>
       </c>
@@ -3837,7 +3922,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3">
       <c r="A268" s="6" t="s">
         <v>114</v>
       </c>
@@ -3848,7 +3933,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3">
       <c r="A269" s="3" t="s">
         <v>1</v>
       </c>
@@ -3859,7 +3944,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3">
       <c r="A270" s="6" t="s">
         <v>113</v>
       </c>
@@ -3870,7 +3955,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3">
       <c r="A271" s="6" t="s">
         <v>110</v>
       </c>
@@ -3881,7 +3966,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3">
       <c r="A272" s="3" t="s">
         <v>1</v>
       </c>
@@ -3892,7 +3977,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3">
       <c r="A273" s="6" t="s">
         <v>112</v>
       </c>
@@ -3903,7 +3988,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3">
       <c r="A274" s="3" t="s">
         <v>1</v>
       </c>
@@ -3914,7 +3999,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3">
       <c r="A275" s="6" t="s">
         <v>117</v>
       </c>
@@ -3925,7 +4010,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3">
       <c r="A276" s="6" t="s">
         <v>116</v>
       </c>
@@ -3936,7 +4021,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3">
       <c r="A277" s="3" t="s">
         <v>1</v>
       </c>
@@ -3947,7 +4032,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3">
       <c r="A278" s="6" t="s">
         <v>113</v>
       </c>
@@ -3958,7 +4043,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3">
       <c r="A279" t="s">
         <v>1</v>
       </c>
@@ -3969,7 +4054,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3">
       <c r="A280" t="s">
         <v>121</v>
       </c>
@@ -3980,7 +4065,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3">
       <c r="A281" t="s">
         <v>12</v>
       </c>
@@ -3991,7 +4076,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3">
       <c r="A282" t="s">
         <v>13</v>
       </c>
@@ -4002,7 +4087,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3">
       <c r="A283" t="s">
         <v>20</v>
       </c>
@@ -4013,7 +4098,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3">
       <c r="A284" t="s">
         <v>21</v>
       </c>
@@ -4024,7 +4109,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3">
       <c r="A285" t="s">
         <v>14</v>
       </c>
@@ -4035,7 +4120,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3">
       <c r="A286" t="s">
         <v>15</v>
       </c>
@@ -4046,7 +4131,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -4057,7 +4142,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3">
       <c r="A288" t="s">
         <v>17</v>
       </c>
@@ -4068,7 +4153,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3">
       <c r="A289" t="s">
         <v>19</v>
       </c>
@@ -4079,7 +4164,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3">
       <c r="A290" t="s">
         <v>1</v>
       </c>
@@ -4090,7 +4175,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3">
       <c r="A291" t="s">
         <v>113</v>
       </c>
@@ -4101,7 +4186,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3">
       <c r="A292" t="s">
         <v>1</v>
       </c>
@@ -4112,7 +4197,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3">
       <c r="A293" t="s">
         <v>111</v>
       </c>
@@ -4123,7 +4208,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3">
       <c r="A294" t="s">
         <v>138</v>
       </c>
@@ -4134,7 +4219,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3">
       <c r="A295" t="s">
         <v>137</v>
       </c>
@@ -4145,7 +4230,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3">
       <c r="A296" t="s">
         <v>1</v>
       </c>
@@ -4156,7 +4241,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3">
       <c r="A297" t="s">
         <v>2</v>
       </c>
@@ -4167,7 +4252,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3">
       <c r="A298" t="s">
         <v>120</v>
       </c>
@@ -4178,7 +4263,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3">
       <c r="A299" t="s">
         <v>3</v>
       </c>
@@ -4189,7 +4274,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3">
       <c r="A300" t="s">
         <v>4</v>
       </c>
@@ -4200,7 +4285,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3">
       <c r="A301" t="s">
         <v>5</v>
       </c>
@@ -4211,7 +4296,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3">
       <c r="A302" t="s">
         <v>7</v>
       </c>
@@ -4222,7 +4307,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3">
       <c r="A303" t="s">
         <v>9</v>
       </c>
@@ -4233,7 +4318,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3">
       <c r="A304" t="s">
         <v>10</v>
       </c>
@@ -4244,7 +4329,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3">
       <c r="A305" t="s">
         <v>11</v>
       </c>
@@ -4255,7 +4340,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3">
       <c r="A306" t="s">
         <v>1</v>
       </c>
@@ -4266,7 +4351,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3">
       <c r="A307" t="s">
         <v>112</v>
       </c>
@@ -4277,7 +4362,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3">
       <c r="A308" t="s">
         <v>1</v>
       </c>
@@ -4288,7 +4373,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3">
       <c r="A309" t="s">
         <v>87</v>
       </c>
@@ -4299,7 +4384,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3">
       <c r="A310" t="s">
         <v>1</v>
       </c>
@@ -4310,7 +4395,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3">
       <c r="A311" t="s">
         <v>114</v>
       </c>
@@ -4321,7 +4406,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3">
       <c r="A312" t="s">
         <v>1</v>
       </c>
@@ -4332,7 +4417,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3">
       <c r="A313" t="s">
         <v>117</v>
       </c>
@@ -4343,7 +4428,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3">
       <c r="A314" t="s">
         <v>1</v>
       </c>
@@ -4354,7 +4439,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3">
       <c r="A315" t="s">
         <v>22</v>
       </c>
@@ -4365,7 +4450,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3">
       <c r="A316" t="s">
         <v>23</v>
       </c>
@@ -4376,7 +4461,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3">
       <c r="A317" t="s">
         <v>122</v>
       </c>
@@ -4387,7 +4472,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3">
       <c r="A318" t="s">
         <v>24</v>
       </c>
@@ -4398,7 +4483,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3">
       <c r="A319" t="s">
         <v>25</v>
       </c>
@@ -4409,7 +4494,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3">
       <c r="A320" t="s">
         <v>123</v>
       </c>
@@ -4420,7 +4505,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3">
       <c r="A321" t="s">
         <v>27</v>
       </c>
@@ -4431,7 +4516,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3">
       <c r="A322" t="s">
         <v>124</v>
       </c>
@@ -4442,7 +4527,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3">
       <c r="A323" t="s">
         <v>125</v>
       </c>
@@ -4453,7 +4538,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3">
       <c r="A324" t="s">
         <v>126</v>
       </c>
@@ -4464,7 +4549,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3">
       <c r="A325" t="s">
         <v>139</v>
       </c>
@@ -4475,7 +4560,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3">
       <c r="A326" t="s">
         <v>128</v>
       </c>
@@ -4486,7 +4571,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3">
       <c r="A327" t="s">
         <v>140</v>
       </c>
@@ -4497,7 +4582,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3">
       <c r="A328" t="s">
         <v>129</v>
       </c>
@@ -4508,7 +4593,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3">
       <c r="A329" t="s">
         <v>32</v>
       </c>
@@ -4519,7 +4604,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3">
       <c r="A330" t="s">
         <v>34</v>
       </c>
@@ -4530,7 +4615,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3">
       <c r="A331" t="s">
         <v>130</v>
       </c>
@@ -4541,7 +4626,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3">
       <c r="A332" t="s">
         <v>131</v>
       </c>
@@ -4552,7 +4637,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3">
       <c r="A333" t="s">
         <v>35</v>
       </c>
@@ -4563,7 +4648,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3">
       <c r="A334" t="s">
         <v>36</v>
       </c>
@@ -4574,7 +4659,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3">
       <c r="A335" t="s">
         <v>43</v>
       </c>
@@ -4585,7 +4670,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3">
       <c r="A336" t="s">
         <v>38</v>
       </c>
@@ -4596,7 +4681,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3">
       <c r="A337" t="s">
         <v>132</v>
       </c>
@@ -4607,7 +4692,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3">
       <c r="A338" t="s">
         <v>39</v>
       </c>
@@ -4618,7 +4703,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3">
       <c r="A339" t="s">
         <v>46</v>
       </c>
@@ -4629,7 +4714,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -4640,7 +4725,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3">
       <c r="A341" t="s">
         <v>141</v>
       </c>
@@ -4651,7 +4736,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3">
       <c r="A342" t="s">
         <v>142</v>
       </c>
@@ -4662,7 +4747,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3">
       <c r="A343" t="s">
         <v>41</v>
       </c>
@@ -4673,7 +4758,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3">
       <c r="A344" t="s">
         <v>42</v>
       </c>
@@ -4684,7 +4769,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3">
       <c r="A345" t="s">
         <v>18</v>
       </c>
@@ -4695,7 +4780,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3">
       <c r="A346" t="s">
         <v>133</v>
       </c>
@@ -4706,7 +4791,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3">
       <c r="A347" t="s">
         <v>1</v>
       </c>
@@ -4717,7 +4802,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3">
       <c r="A348" t="s">
         <v>103</v>
       </c>
@@ -4728,7 +4813,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3">
       <c r="A349" t="s">
         <v>109</v>
       </c>
@@ -4739,7 +4824,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3">
       <c r="A350" t="s">
         <v>104</v>
       </c>
@@ -4750,7 +4835,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3">
       <c r="A351" t="s">
         <v>47</v>
       </c>
@@ -4761,7 +4846,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3">
       <c r="A352" t="s">
         <v>106</v>
       </c>
@@ -4772,7 +4857,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3">
       <c r="A353" t="s">
         <v>107</v>
       </c>
@@ -4783,7 +4868,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3">
       <c r="A354" t="s">
         <v>108</v>
       </c>
@@ -4794,7 +4879,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3">
       <c r="A355" t="s">
         <v>1</v>
       </c>
@@ -4805,7 +4890,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3">
       <c r="A356" t="s">
         <v>86</v>
       </c>
@@ -4816,7 +4901,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3">
       <c r="A357" t="s">
         <v>48</v>
       </c>
@@ -4827,7 +4912,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3">
       <c r="A358" t="s">
         <v>143</v>
       </c>
@@ -4838,7 +4923,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3">
       <c r="A359" t="s">
         <v>50</v>
       </c>
@@ -4849,7 +4934,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3">
       <c r="A360" t="s">
         <v>144</v>
       </c>
@@ -4860,7 +4945,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3">
       <c r="A361" t="s">
         <v>51</v>
       </c>
@@ -4871,7 +4956,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3">
       <c r="A362" t="s">
         <v>52</v>
       </c>
@@ -4882,7 +4967,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3">
       <c r="A363" t="s">
         <v>53</v>
       </c>
@@ -4893,7 +4978,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3">
       <c r="A364" t="s">
         <v>145</v>
       </c>
@@ -4904,7 +4989,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3">
       <c r="A365" t="s">
         <v>146</v>
       </c>
@@ -4915,7 +5000,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3">
       <c r="A366" t="s">
         <v>57</v>
       </c>
@@ -4926,7 +5011,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3">
       <c r="A367" t="s">
         <v>92</v>
       </c>
@@ -4937,7 +5022,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3">
       <c r="A368" t="s">
         <v>59</v>
       </c>
@@ -4948,7 +5033,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3">
       <c r="A369" t="s">
         <v>60</v>
       </c>
@@ -4959,7 +5044,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:3">
       <c r="A370" t="s">
         <v>62</v>
       </c>
@@ -4970,7 +5055,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3">
       <c r="A371" t="s">
         <v>63</v>
       </c>
@@ -4981,7 +5066,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:3">
       <c r="A372" t="s">
         <v>64</v>
       </c>
@@ -4992,7 +5077,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:3">
       <c r="A373" t="s">
         <v>66</v>
       </c>
@@ -5003,7 +5088,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:3">
       <c r="A374" t="s">
         <v>67</v>
       </c>
@@ -5014,7 +5099,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:3">
       <c r="A375" t="s">
         <v>147</v>
       </c>
@@ -5025,7 +5110,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:3">
       <c r="A376" t="s">
         <v>89</v>
       </c>
@@ -5036,7 +5121,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:3">
       <c r="A377" t="s">
         <v>94</v>
       </c>
@@ -5047,7 +5132,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:3">
       <c r="A378" t="s">
         <v>70</v>
       </c>
@@ -5058,7 +5143,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:3">
       <c r="A379" t="s">
         <v>134</v>
       </c>
@@ -5069,7 +5154,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:3">
       <c r="A380" t="s">
         <v>90</v>
       </c>
@@ -5080,7 +5165,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:3">
       <c r="A381" t="s">
         <v>71</v>
       </c>
@@ -5091,7 +5176,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:3">
       <c r="A382" t="s">
         <v>73</v>
       </c>
@@ -5102,7 +5187,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:3">
       <c r="A383" t="s">
         <v>87</v>
       </c>
@@ -5113,7 +5198,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:3">
       <c r="A384" t="s">
         <v>135</v>
       </c>
@@ -5124,7 +5209,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:3">
       <c r="A385" t="s">
         <v>74</v>
       </c>
@@ -5135,7 +5220,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:3">
       <c r="A386" t="s">
         <v>76</v>
       </c>
@@ -5146,7 +5231,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:3">
       <c r="A387" t="s">
         <v>148</v>
       </c>
@@ -5157,7 +5242,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:3">
       <c r="A388" t="s">
         <v>98</v>
       </c>
@@ -5168,7 +5253,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:3">
       <c r="A389" t="s">
         <v>99</v>
       </c>
@@ -5179,7 +5264,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:3">
       <c r="A390" t="s">
         <v>149</v>
       </c>
@@ -5190,7 +5275,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:3">
       <c r="A391" t="s">
         <v>102</v>
       </c>
@@ -5201,7 +5286,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3">
       <c r="A392" t="s">
         <v>79</v>
       </c>
@@ -5212,7 +5297,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:3">
       <c r="A393" t="s">
         <v>150</v>
       </c>
@@ -5223,7 +5308,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:3">
       <c r="A394" t="s">
         <v>136</v>
       </c>
@@ -5234,7 +5319,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:3">
       <c r="A395" t="s">
         <v>82</v>
       </c>
@@ -5245,7 +5330,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3">
       <c r="A396" t="s">
         <v>83</v>
       </c>
@@ -5256,7 +5341,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:3">
       <c r="A397" t="s">
         <v>88</v>
       </c>
@@ -5267,7 +5352,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:3">
       <c r="A398" t="s">
         <v>93</v>
       </c>
@@ -5278,7 +5363,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3">
       <c r="A399" t="s">
         <v>95</v>
       </c>
@@ -5289,7 +5374,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:3">
       <c r="A400" t="s">
         <v>96</v>
       </c>
@@ -5300,7 +5385,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:3">
       <c r="A401" t="s">
         <v>151</v>
       </c>
@@ -5311,7 +5396,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:3">
       <c r="A402" t="s">
         <v>97</v>
       </c>
@@ -5322,7 +5407,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:3">
       <c r="A403" t="s">
         <v>44</v>
       </c>
@@ -5333,7 +5418,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:3">
       <c r="A404" t="s">
         <v>85</v>
       </c>
@@ -5344,7 +5429,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:3">
       <c r="A405" t="s">
         <v>100</v>
       </c>
@@ -5355,7 +5440,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:3">
       <c r="A406" t="s">
         <v>69</v>
       </c>
@@ -5366,7 +5451,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:3">
       <c r="A407" t="s">
         <v>49</v>
       </c>
@@ -5377,7 +5462,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:3">
       <c r="A408" t="s">
         <v>84</v>
       </c>
@@ -5388,7 +5473,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:3">
       <c r="A409" s="6" t="s">
         <v>113</v>
       </c>
@@ -5399,7 +5484,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:3">
       <c r="A410" s="3" t="s">
         <v>1</v>
       </c>
@@ -5410,7 +5495,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:3">
       <c r="A411" s="6" t="s">
         <v>7</v>
       </c>
@@ -5421,7 +5506,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:3">
       <c r="A412" s="6" t="s">
         <v>152</v>
       </c>
@@ -5432,7 +5517,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:3">
       <c r="A413" s="6" t="s">
         <v>9</v>
       </c>
@@ -5443,7 +5528,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:3">
       <c r="A414" s="6" t="s">
         <v>11</v>
       </c>
@@ -5454,7 +5539,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:3">
       <c r="A415" s="6" t="s">
         <v>4</v>
       </c>
@@ -5465,7 +5550,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:3">
       <c r="A416" s="6" t="s">
         <v>3</v>
       </c>
@@ -5476,7 +5561,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:3">
       <c r="A417" s="6" t="s">
         <v>10</v>
       </c>
@@ -5487,7 +5572,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:3">
       <c r="A418" s="6" t="s">
         <v>2</v>
       </c>
@@ -5498,7 +5583,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:3">
       <c r="A419" s="6" t="s">
         <v>5</v>
       </c>
@@ -5509,7 +5594,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:3">
       <c r="A420" s="3" t="s">
         <v>1</v>
       </c>
@@ -5520,7 +5605,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:3">
       <c r="A421" s="6" t="s">
         <v>15</v>
       </c>
@@ -5531,7 +5616,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:3">
       <c r="A422" s="6" t="s">
         <v>19</v>
       </c>
@@ -5542,7 +5627,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:3">
       <c r="A423" s="6" t="s">
         <v>12</v>
       </c>
@@ -5553,7 +5638,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:3">
       <c r="A424" s="6" t="s">
         <v>20</v>
       </c>
@@ -5564,7 +5649,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:3">
       <c r="A425" s="6" t="s">
         <v>21</v>
       </c>
@@ -5575,7 +5660,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:3">
       <c r="A426" s="6" t="s">
         <v>16</v>
       </c>
@@ -5586,7 +5671,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:3">
       <c r="A427" s="6" t="s">
         <v>14</v>
       </c>
@@ -5597,7 +5682,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:3">
       <c r="A428" s="6" t="s">
         <v>153</v>
       </c>
@@ -5608,7 +5693,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:3">
       <c r="A429" s="6" t="s">
         <v>17</v>
       </c>
@@ -5619,7 +5704,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:3">
       <c r="A430" s="6" t="s">
         <v>154</v>
       </c>
@@ -5630,7 +5715,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:3">
       <c r="A431" s="6" t="s">
         <v>121</v>
       </c>
@@ -5641,7 +5726,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:3">
       <c r="A432" s="3" t="s">
         <v>1</v>
       </c>
@@ -5652,7 +5737,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:3">
       <c r="A433" s="6" t="s">
         <v>155</v>
       </c>
@@ -5663,7 +5748,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:3">
       <c r="A434" s="6" t="s">
         <v>38</v>
       </c>
@@ -5674,7 +5759,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:3">
       <c r="A435" s="6" t="s">
         <v>132</v>
       </c>
@@ -5685,7 +5770,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:3">
       <c r="A436" s="6" t="s">
         <v>142</v>
       </c>
@@ -5696,7 +5781,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:3">
       <c r="A437" s="6" t="s">
         <v>130</v>
       </c>
@@ -5707,7 +5792,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:3">
       <c r="A438" s="6" t="s">
         <v>22</v>
       </c>
@@ -5718,7 +5803,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:3">
       <c r="A439" s="6" t="s">
         <v>24</v>
       </c>
@@ -5729,7 +5814,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:3">
       <c r="A440" s="6" t="s">
         <v>126</v>
       </c>
@@ -5740,7 +5825,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:3">
       <c r="A441" s="6" t="s">
         <v>128</v>
       </c>
@@ -5751,7 +5836,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:3">
       <c r="A442" s="6" t="s">
         <v>36</v>
       </c>
@@ -5762,7 +5847,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:3">
       <c r="A443" s="6" t="s">
         <v>123</v>
       </c>
@@ -5773,7 +5858,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:3">
       <c r="A444" s="6" t="s">
         <v>133</v>
       </c>
@@ -5784,7 +5869,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:3">
       <c r="A445" s="6" t="s">
         <v>40</v>
       </c>
@@ -5795,7 +5880,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:3">
       <c r="A446" s="6" t="s">
         <v>139</v>
       </c>
@@ -5806,7 +5891,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:3">
       <c r="A447" s="6" t="s">
         <v>46</v>
       </c>
@@ -5817,7 +5902,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:3">
       <c r="A448" s="6" t="s">
         <v>156</v>
       </c>
@@ -5828,7 +5913,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:3">
       <c r="A449" s="6" t="s">
         <v>27</v>
       </c>
@@ -5839,7 +5924,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:3">
       <c r="A450" s="6" t="s">
         <v>131</v>
       </c>
@@ -5850,7 +5935,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:3">
       <c r="A451" s="6" t="s">
         <v>43</v>
       </c>
@@ -5861,7 +5946,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:3">
       <c r="A452" s="6" t="s">
         <v>35</v>
       </c>
@@ -5872,7 +5957,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:3">
       <c r="A453" s="6" t="s">
         <v>39</v>
       </c>
@@ -5883,7 +5968,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:3">
       <c r="A454" s="6" t="s">
         <v>42</v>
       </c>
@@ -5894,7 +5979,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:3">
       <c r="A455" s="6" t="s">
         <v>141</v>
       </c>
@@ -5905,7 +5990,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:3">
       <c r="A456" s="6" t="s">
         <v>140</v>
       </c>
@@ -5916,7 +6001,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:3">
       <c r="A457" s="6" t="s">
         <v>34</v>
       </c>
@@ -5927,7 +6012,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:3">
       <c r="A458" s="6" t="s">
         <v>18</v>
       </c>
@@ -5938,7 +6023,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:3">
       <c r="A459" s="6" t="s">
         <v>23</v>
       </c>
@@ -5949,7 +6034,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:3">
       <c r="A460" s="6" t="s">
         <v>25</v>
       </c>
@@ -5960,7 +6045,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:3">
       <c r="A461" s="6" t="s">
         <v>32</v>
       </c>
@@ -5971,7 +6056,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:3">
       <c r="A462" s="6" t="s">
         <v>124</v>
       </c>
@@ -5982,7 +6067,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:3">
       <c r="A463" s="3" t="s">
         <v>1</v>
       </c>
@@ -5993,7 +6078,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:3">
       <c r="A464" s="6" t="s">
         <v>109</v>
       </c>
@@ -6004,7 +6089,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:3">
       <c r="A465" s="6" t="s">
         <v>108</v>
       </c>
@@ -6015,7 +6100,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:3">
       <c r="A466" s="6" t="s">
         <v>103</v>
       </c>
@@ -6026,7 +6111,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:3">
       <c r="A467" s="6" t="s">
         <v>104</v>
       </c>
@@ -6037,7 +6122,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:3">
       <c r="A468" s="6" t="s">
         <v>107</v>
       </c>
@@ -6048,7 +6133,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:3">
       <c r="A469" s="6" t="s">
         <v>106</v>
       </c>
@@ -6059,7 +6144,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:3">
       <c r="A470" s="6" t="s">
         <v>47</v>
       </c>
@@ -6070,7 +6155,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:3">
       <c r="A471" s="3" t="s">
         <v>1</v>
       </c>
@@ -6081,7 +6166,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:3">
       <c r="A472" s="6" t="s">
         <v>64</v>
       </c>
@@ -6092,7 +6177,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:3">
       <c r="A473" s="6" t="s">
         <v>94</v>
       </c>
@@ -6103,7 +6188,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:3">
       <c r="A474" s="6" t="s">
         <v>70</v>
       </c>
@@ -6114,7 +6199,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:3">
       <c r="A475" s="6" t="s">
         <v>73</v>
       </c>
@@ -6125,7 +6210,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:3">
       <c r="A476" s="6" t="s">
         <v>149</v>
       </c>
@@ -6136,7 +6221,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:3">
       <c r="A477" s="6" t="s">
         <v>82</v>
       </c>
@@ -6147,7 +6232,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:3">
       <c r="A478" s="6" t="s">
         <v>95</v>
       </c>
@@ -6158,7 +6243,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:3">
       <c r="A479" s="6" t="s">
         <v>151</v>
       </c>
@@ -6169,7 +6254,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:3">
       <c r="A480" s="6" t="s">
         <v>144</v>
       </c>
@@ -6180,7 +6265,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:3">
       <c r="A481" s="6" t="s">
         <v>146</v>
       </c>
@@ -6191,7 +6276,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:3">
       <c r="A482" s="6" t="s">
         <v>86</v>
       </c>
@@ -6202,7 +6287,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:3">
       <c r="A483" s="6" t="s">
         <v>76</v>
       </c>
@@ -6213,7 +6298,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:3">
       <c r="A484" s="6" t="s">
         <v>61</v>
       </c>
@@ -6224,7 +6309,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:3">
       <c r="A485" s="6" t="s">
         <v>63</v>
       </c>
@@ -6235,7 +6320,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:3">
       <c r="A486" s="6" t="s">
         <v>69</v>
       </c>
@@ -6246,7 +6331,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:3">
       <c r="A487" s="6" t="s">
         <v>135</v>
       </c>
@@ -6257,7 +6342,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:3">
       <c r="A488" s="6" t="s">
         <v>148</v>
       </c>
@@ -6268,7 +6353,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:3">
       <c r="A489" s="6" t="s">
         <v>83</v>
       </c>
@@ -6279,7 +6364,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:3">
       <c r="A490" s="6" t="s">
         <v>84</v>
       </c>
@@ -6290,7 +6375,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:3">
       <c r="A491" s="6" t="s">
         <v>71</v>
       </c>
@@ -6301,7 +6386,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:3">
       <c r="A492" s="6" t="s">
         <v>97</v>
       </c>
@@ -6312,7 +6397,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:3">
       <c r="A493" s="6" t="s">
         <v>90</v>
       </c>
@@ -6323,7 +6408,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:3">
       <c r="A494" s="6" t="s">
         <v>60</v>
       </c>
@@ -6334,7 +6419,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:3">
       <c r="A495" s="6" t="s">
         <v>93</v>
       </c>
@@ -6345,7 +6430,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:3">
       <c r="A496" s="6" t="s">
         <v>85</v>
       </c>
@@ -6356,7 +6441,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:3">
       <c r="A497" s="6" t="s">
         <v>53</v>
       </c>
@@ -6367,7 +6452,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:3">
       <c r="A498" s="6" t="s">
         <v>147</v>
       </c>
@@ -6378,7 +6463,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:3">
       <c r="A499" s="6" t="s">
         <v>50</v>
       </c>
@@ -6389,7 +6474,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:3">
       <c r="A500" s="6" t="s">
         <v>51</v>
       </c>
@@ -6400,7 +6485,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:3">
       <c r="A501" s="6" t="s">
         <v>52</v>
       </c>
@@ -6411,7 +6496,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:3">
       <c r="A502" s="6" t="s">
         <v>145</v>
       </c>
@@ -6422,7 +6507,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:3">
       <c r="A503" s="6" t="s">
         <v>59</v>
       </c>
@@ -6433,7 +6518,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:3">
       <c r="A504" s="6" t="s">
         <v>66</v>
       </c>
@@ -6444,7 +6529,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:3">
       <c r="A505" s="6" t="s">
         <v>49</v>
       </c>
@@ -6455,7 +6540,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:3">
       <c r="A506" s="6" t="s">
         <v>100</v>
       </c>
@@ -6466,7 +6551,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:3">
       <c r="A507" s="6" t="s">
         <v>89</v>
       </c>
@@ -6477,7 +6562,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:3">
       <c r="A508" s="6" t="s">
         <v>134</v>
       </c>
@@ -6488,7 +6573,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:3">
       <c r="A509" s="6" t="s">
         <v>62</v>
       </c>
@@ -6499,7 +6584,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:3">
       <c r="A510" s="6" t="s">
         <v>44</v>
       </c>
@@ -6510,7 +6595,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:3">
       <c r="A511" s="6" t="s">
         <v>88</v>
       </c>
@@ -6521,7 +6606,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:3">
       <c r="A512" s="6" t="s">
         <v>96</v>
       </c>
@@ -6532,7 +6617,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:3">
       <c r="A513" s="6" t="s">
         <v>99</v>
       </c>
@@ -6543,7 +6628,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:3">
       <c r="A514" s="6" t="s">
         <v>102</v>
       </c>
@@ -6554,7 +6639,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:3">
       <c r="A515" s="6" t="s">
         <v>157</v>
       </c>
@@ -6565,7 +6650,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:3">
       <c r="A516" s="6" t="s">
         <v>150</v>
       </c>
@@ -6576,7 +6661,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:3">
       <c r="A517" s="6" t="s">
         <v>92</v>
       </c>
@@ -6587,7 +6672,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:3">
       <c r="A518" s="6" t="s">
         <v>79</v>
       </c>
@@ -6598,7 +6683,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:3">
       <c r="A519" s="6" t="s">
         <v>74</v>
       </c>
@@ -6609,7 +6694,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:3">
       <c r="A520" s="6" t="s">
         <v>98</v>
       </c>
@@ -6620,7 +6705,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:3">
       <c r="A521" s="6" t="s">
         <v>48</v>
       </c>
@@ -6631,7 +6716,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:3">
       <c r="A522" s="6" t="s">
         <v>57</v>
       </c>
@@ -6642,7 +6727,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:3">
       <c r="A523" s="6" t="s">
         <v>77</v>
       </c>
@@ -6653,7 +6738,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:3">
       <c r="A524" s="3" t="s">
         <v>1</v>
       </c>
@@ -6664,7 +6749,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:3">
       <c r="A525" s="6" t="s">
         <v>111</v>
       </c>
@@ -6675,7 +6760,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:3">
       <c r="A526" s="6" t="s">
         <v>138</v>
       </c>
@@ -6686,7 +6771,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:3">
       <c r="A527" s="6" t="s">
         <v>137</v>
       </c>
@@ -6697,7 +6782,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:3">
       <c r="A528" s="3" t="s">
         <v>1</v>
       </c>
@@ -6708,7 +6793,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:3">
       <c r="A529" s="6" t="s">
         <v>117</v>
       </c>
@@ -6719,7 +6804,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:3">
       <c r="A530" s="3" t="s">
         <v>1</v>
       </c>
@@ -6730,7 +6815,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:3">
       <c r="A531" s="6" t="s">
         <v>112</v>
       </c>
@@ -6741,7 +6826,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:3">
       <c r="A532" s="3" t="s">
         <v>1</v>
       </c>
@@ -6752,7 +6837,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:3">
       <c r="A533" s="6" t="s">
         <v>114</v>
       </c>
@@ -6761,6 +6846,1491 @@
       </c>
       <c r="C533" s="8">
         <v>46113</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3">
+      <c r="A534" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B534" s="12">
+        <v>1</v>
+      </c>
+      <c r="C534" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3">
+      <c r="A535" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B535" s="13">
+        <v>1</v>
+      </c>
+      <c r="C535" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3">
+      <c r="A536" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B536" s="13">
+        <v>1</v>
+      </c>
+      <c r="C536" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3">
+      <c r="A537" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B537" s="13">
+        <v>1</v>
+      </c>
+      <c r="C537" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3">
+      <c r="A538" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B538" s="13">
+        <v>1</v>
+      </c>
+      <c r="C538" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3">
+      <c r="A539" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B539" s="13">
+        <v>1</v>
+      </c>
+      <c r="C539" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3">
+      <c r="A540" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B540" s="13">
+        <v>1</v>
+      </c>
+      <c r="C540" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3">
+      <c r="A541" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B541" s="13">
+        <v>1</v>
+      </c>
+      <c r="C541" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3">
+      <c r="A542" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B542" s="13">
+        <v>1</v>
+      </c>
+      <c r="C542" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3">
+      <c r="A543" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B543" s="13">
+        <v>1</v>
+      </c>
+      <c r="C543" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3">
+      <c r="A544" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B544" s="13">
+        <v>1</v>
+      </c>
+      <c r="C544" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3">
+      <c r="A545" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B545" s="13">
+        <v>1</v>
+      </c>
+      <c r="C545" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3">
+      <c r="A546" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B546" s="12">
+        <v>1</v>
+      </c>
+      <c r="C546" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3">
+      <c r="A547" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B547" s="13">
+        <v>1</v>
+      </c>
+      <c r="C547" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3">
+      <c r="A548" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B548" s="12">
+        <v>1</v>
+      </c>
+      <c r="C548" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3">
+      <c r="A549" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B549" s="13">
+        <v>1</v>
+      </c>
+      <c r="C549" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3">
+      <c r="A550" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B550" s="13">
+        <v>1</v>
+      </c>
+      <c r="C550" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3">
+      <c r="A551" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B551" s="13">
+        <v>1</v>
+      </c>
+      <c r="C551" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3">
+      <c r="A552" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B552" s="12">
+        <v>1</v>
+      </c>
+      <c r="C552" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3">
+      <c r="A553" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B553" s="13">
+        <v>1</v>
+      </c>
+      <c r="C553" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3">
+      <c r="A554" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B554" s="12">
+        <v>1</v>
+      </c>
+      <c r="C554" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3">
+      <c r="A555" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B555" s="13">
+        <v>1</v>
+      </c>
+      <c r="C555" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3">
+      <c r="A556" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B556" s="13">
+        <v>1</v>
+      </c>
+      <c r="C556" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3">
+      <c r="A557" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B557" s="13">
+        <v>1</v>
+      </c>
+      <c r="C557" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3">
+      <c r="A558" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B558" s="13">
+        <v>1</v>
+      </c>
+      <c r="C558" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3">
+      <c r="A559" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B559" s="13">
+        <v>1</v>
+      </c>
+      <c r="C559" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3">
+      <c r="A560" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B560" s="13">
+        <v>1</v>
+      </c>
+      <c r="C560" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3">
+      <c r="A561" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B561" s="13">
+        <v>1</v>
+      </c>
+      <c r="C561" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3">
+      <c r="A562" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B562" s="13">
+        <v>1</v>
+      </c>
+      <c r="C562" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3">
+      <c r="A563" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B563" s="13">
+        <v>1</v>
+      </c>
+      <c r="C563" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3">
+      <c r="A564" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B564" s="12">
+        <v>1</v>
+      </c>
+      <c r="C564" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3">
+      <c r="A565" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B565" s="13">
+        <v>1</v>
+      </c>
+      <c r="C565" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3">
+      <c r="A566" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B566" s="12">
+        <v>1</v>
+      </c>
+      <c r="C566" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3">
+      <c r="A567" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B567" s="13">
+        <v>1</v>
+      </c>
+      <c r="C567" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3">
+      <c r="A568" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B568" s="12">
+        <v>0.99831365935919059</v>
+      </c>
+      <c r="C568" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3">
+      <c r="A569" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B569" s="13">
+        <v>1</v>
+      </c>
+      <c r="C569" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3">
+      <c r="A570" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B570" s="13">
+        <v>1</v>
+      </c>
+      <c r="C570" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3">
+      <c r="A571" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B571" s="13">
+        <v>1</v>
+      </c>
+      <c r="C571" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3">
+      <c r="A572" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B572" s="13">
+        <v>1</v>
+      </c>
+      <c r="C572" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3">
+      <c r="A573" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B573" s="13">
+        <v>1</v>
+      </c>
+      <c r="C573" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3">
+      <c r="A574" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B574" s="13">
+        <v>1</v>
+      </c>
+      <c r="C574" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3">
+      <c r="A575" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B575" s="13">
+        <v>1</v>
+      </c>
+      <c r="C575" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3">
+      <c r="A576" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B576" s="13">
+        <v>1</v>
+      </c>
+      <c r="C576" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3">
+      <c r="A577" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B577" s="13">
+        <v>1</v>
+      </c>
+      <c r="C577" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3">
+      <c r="A578" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B578" s="13">
+        <v>1</v>
+      </c>
+      <c r="C578" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3">
+      <c r="A579" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B579" s="13">
+        <v>1</v>
+      </c>
+      <c r="C579" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3">
+      <c r="A580" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B580" s="13">
+        <v>1</v>
+      </c>
+      <c r="C580" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3">
+      <c r="A581" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B581" s="13">
+        <v>1</v>
+      </c>
+      <c r="C581" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3">
+      <c r="A582" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B582" s="13">
+        <v>1</v>
+      </c>
+      <c r="C582" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3">
+      <c r="A583" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B583" s="13">
+        <v>1</v>
+      </c>
+      <c r="C583" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3">
+      <c r="A584" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B584" s="13">
+        <v>1</v>
+      </c>
+      <c r="C584" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3">
+      <c r="A585" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B585" s="13">
+        <v>1</v>
+      </c>
+      <c r="C585" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3">
+      <c r="A586" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B586" s="13">
+        <v>1</v>
+      </c>
+      <c r="C586" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3">
+      <c r="A587" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B587" s="13">
+        <v>1</v>
+      </c>
+      <c r="C587" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3">
+      <c r="A588" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B588" s="13">
+        <v>1</v>
+      </c>
+      <c r="C588" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3">
+      <c r="A589" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B589" s="13">
+        <v>1</v>
+      </c>
+      <c r="C589" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3">
+      <c r="A590" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B590" s="13">
+        <v>1</v>
+      </c>
+      <c r="C590" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3">
+      <c r="A591" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B591" s="13">
+        <v>1</v>
+      </c>
+      <c r="C591" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3">
+      <c r="A592" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B592" s="13">
+        <v>1</v>
+      </c>
+      <c r="C592" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3">
+      <c r="A593" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B593" s="13">
+        <v>1</v>
+      </c>
+      <c r="C593" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3">
+      <c r="A594" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B594" s="13">
+        <v>1</v>
+      </c>
+      <c r="C594" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3">
+      <c r="A595" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B595" s="13">
+        <v>1</v>
+      </c>
+      <c r="C595" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3">
+      <c r="A596" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B596" s="13">
+        <v>1</v>
+      </c>
+      <c r="C596" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3">
+      <c r="A597" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B597" s="13">
+        <v>1</v>
+      </c>
+      <c r="C597" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3">
+      <c r="A598" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B598" s="13">
+        <v>1</v>
+      </c>
+      <c r="C598" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3">
+      <c r="A599" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B599" s="13">
+        <v>1</v>
+      </c>
+      <c r="C599" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3">
+      <c r="A600" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B600" s="13">
+        <v>1</v>
+      </c>
+      <c r="C600" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3">
+      <c r="A601" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B601" s="13">
+        <v>1</v>
+      </c>
+      <c r="C601" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3">
+      <c r="A602" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B602" s="13">
+        <v>1</v>
+      </c>
+      <c r="C602" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3">
+      <c r="A603" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B603" s="13">
+        <v>1</v>
+      </c>
+      <c r="C603" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3">
+      <c r="A604" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B604" s="13">
+        <v>1</v>
+      </c>
+      <c r="C604" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3">
+      <c r="A605" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B605" s="13">
+        <v>1</v>
+      </c>
+      <c r="C605" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3">
+      <c r="A606" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B606" s="13">
+        <v>1</v>
+      </c>
+      <c r="C606" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3">
+      <c r="A607" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B607" s="13">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C607" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3">
+      <c r="A608" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B608" s="12">
+        <v>0.98403193612774453</v>
+      </c>
+      <c r="C608" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3">
+      <c r="A609" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B609" s="13">
+        <v>1</v>
+      </c>
+      <c r="C609" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3">
+      <c r="A610" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B610" s="13">
+        <v>1</v>
+      </c>
+      <c r="C610" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3">
+      <c r="A611" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B611" s="13">
+        <v>1</v>
+      </c>
+      <c r="C611" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3">
+      <c r="A612" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B612" s="13">
+        <v>1</v>
+      </c>
+      <c r="C612" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3">
+      <c r="A613" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B613" s="13">
+        <v>1</v>
+      </c>
+      <c r="C613" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3">
+      <c r="A614" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B614" s="13">
+        <v>1</v>
+      </c>
+      <c r="C614" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3">
+      <c r="A615" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B615" s="13">
+        <v>1</v>
+      </c>
+      <c r="C615" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3">
+      <c r="A616" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B616" s="13">
+        <v>1</v>
+      </c>
+      <c r="C616" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3">
+      <c r="A617" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B617" s="13">
+        <v>1</v>
+      </c>
+      <c r="C617" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3">
+      <c r="A618" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B618" s="13">
+        <v>1</v>
+      </c>
+      <c r="C618" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3">
+      <c r="A619" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B619" s="13">
+        <v>1</v>
+      </c>
+      <c r="C619" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3">
+      <c r="A620" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B620" s="13">
+        <v>1</v>
+      </c>
+      <c r="C620" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3">
+      <c r="A621" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B621" s="13">
+        <v>1</v>
+      </c>
+      <c r="C621" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3">
+      <c r="A622" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B622" s="13">
+        <v>1</v>
+      </c>
+      <c r="C622" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3">
+      <c r="A623" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B623" s="13">
+        <v>1</v>
+      </c>
+      <c r="C623" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3">
+      <c r="A624" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B624" s="13">
+        <v>1</v>
+      </c>
+      <c r="C624" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3">
+      <c r="A625" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B625" s="13">
+        <v>1</v>
+      </c>
+      <c r="C625" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3">
+      <c r="A626" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B626" s="13">
+        <v>1</v>
+      </c>
+      <c r="C626" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3">
+      <c r="A627" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B627" s="13">
+        <v>1</v>
+      </c>
+      <c r="C627" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3">
+      <c r="A628" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B628" s="13">
+        <v>1</v>
+      </c>
+      <c r="C628" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3">
+      <c r="A629" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B629" s="13">
+        <v>1</v>
+      </c>
+      <c r="C629" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3">
+      <c r="A630" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B630" s="13">
+        <v>1</v>
+      </c>
+      <c r="C630" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3">
+      <c r="A631" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B631" s="13">
+        <v>1</v>
+      </c>
+      <c r="C631" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3">
+      <c r="A632" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B632" s="13">
+        <v>1</v>
+      </c>
+      <c r="C632" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3">
+      <c r="A633" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B633" s="13">
+        <v>1</v>
+      </c>
+      <c r="C633" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3">
+      <c r="A634" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B634" s="13">
+        <v>1</v>
+      </c>
+      <c r="C634" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3">
+      <c r="A635" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B635" s="13">
+        <v>1</v>
+      </c>
+      <c r="C635" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3">
+      <c r="A636" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B636" s="13">
+        <v>1</v>
+      </c>
+      <c r="C636" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3">
+      <c r="A637" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B637" s="13">
+        <v>1</v>
+      </c>
+      <c r="C637" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3">
+      <c r="A638" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B638" s="13">
+        <v>1</v>
+      </c>
+      <c r="C638" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3">
+      <c r="A639" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B639" s="13">
+        <v>1</v>
+      </c>
+      <c r="C639" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3">
+      <c r="A640" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B640" s="13">
+        <v>1</v>
+      </c>
+      <c r="C640" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3">
+      <c r="A641" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B641" s="13">
+        <v>1</v>
+      </c>
+      <c r="C641" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3">
+      <c r="A642" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B642" s="13">
+        <v>1</v>
+      </c>
+      <c r="C642" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3">
+      <c r="A643" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B643" s="13">
+        <v>1</v>
+      </c>
+      <c r="C643" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3">
+      <c r="A644" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B644" s="13">
+        <v>1</v>
+      </c>
+      <c r="C644" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3">
+      <c r="A645" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B645" s="13">
+        <v>1</v>
+      </c>
+      <c r="C645" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3">
+      <c r="A646" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B646" s="13">
+        <v>1</v>
+      </c>
+      <c r="C646" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3">
+      <c r="A647" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B647" s="13">
+        <v>1</v>
+      </c>
+      <c r="C647" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3">
+      <c r="A648" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B648" s="13">
+        <v>1</v>
+      </c>
+      <c r="C648" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3">
+      <c r="A649" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B649" s="13">
+        <v>1</v>
+      </c>
+      <c r="C649" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3">
+      <c r="A650" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B650" s="13">
+        <v>1</v>
+      </c>
+      <c r="C650" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3">
+      <c r="A651" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B651" s="13">
+        <v>1</v>
+      </c>
+      <c r="C651" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3">
+      <c r="A652" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B652" s="13">
+        <v>1</v>
+      </c>
+      <c r="C652" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3">
+      <c r="A653" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B653" s="13">
+        <v>1</v>
+      </c>
+      <c r="C653" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3">
+      <c r="A654" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B654" s="13">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C654" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3">
+      <c r="A655" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B655" s="13">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C655" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3">
+      <c r="A656" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B656" s="13">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C656" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3">
+      <c r="A657" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B657" s="13">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C657" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3">
+      <c r="A658" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B658" s="13">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="C658" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3">
+      <c r="A659" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B659" s="13">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="C659" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3">
+      <c r="A660" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B660" s="13">
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="C660" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3">
+      <c r="A661" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B661" s="12">
+        <v>0.96581196581196582</v>
+      </c>
+      <c r="C661" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3">
+      <c r="A662" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B662" s="13">
+        <v>1</v>
+      </c>
+      <c r="C662" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3">
+      <c r="A663" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B663" s="13">
+        <v>1</v>
+      </c>
+      <c r="C663" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3">
+      <c r="A664" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B664" s="13">
+        <v>1</v>
+      </c>
+      <c r="C664" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3">
+      <c r="A665" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B665" s="13">
+        <v>1</v>
+      </c>
+      <c r="C665" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3">
+      <c r="A666" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B666" s="13">
+        <v>1</v>
+      </c>
+      <c r="C666" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3">
+      <c r="A667" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B667" s="13">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="C667" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3">
+      <c r="A668" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B668" s="13">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="C668" s="8">
+        <v>46143</v>
       </c>
     </row>
   </sheetData>

--- a/data/JLL.xlsx
+++ b/data/JLL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG armazem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8960061B-3CD9-4E47-8B7B-7570FBD469D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC1870E-E8F9-4311-8C21-8623C3973183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JLL" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="193">
   <si>
     <t>% Cumprimento de Jornada</t>
   </si>
@@ -588,13 +588,37 @@
   </si>
   <si>
     <t>WESLEY EDUARDO MATHIAS</t>
+  </si>
+  <si>
+    <t>BRUNO FELIPE DOS PRAZERES CALVETTE</t>
+  </si>
+  <si>
+    <t>ERICK DOS SANTOS DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>LAUDELINO STAPPAZZOLI</t>
+  </si>
+  <si>
+    <t>RAFAEL DA SILVA ANDRADE</t>
+  </si>
+  <si>
+    <t>RICKSON GONCALVES MACEDO</t>
+  </si>
+  <si>
+    <t>GLAUCIA FONSECA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>JOSIEL DE OLIVEIRA CORREIA</t>
+  </si>
+  <si>
+    <t>VITOR MANOEL ASSIS DO NASCIMENTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -610,6 +634,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -650,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -665,6 +694,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -979,15 +1010,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C668"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:C797"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="5" width="27.140625" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="5" width="27.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>118</v>
       </c>
@@ -998,7 +1029,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="4">
         <v>0.89977528089887637</v>
@@ -1007,7 +1038,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1018,7 +1049,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1029,7 +1060,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1040,7 +1071,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1051,7 +1082,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1062,7 +1093,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -1073,7 +1104,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1084,7 +1115,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1095,7 +1126,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1106,7 +1137,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1117,7 +1148,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1128,7 +1159,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
@@ -1139,7 +1170,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -1150,7 +1181,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
@@ -1161,7 +1192,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -1172,7 +1203,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -1183,7 +1214,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -1194,7 +1225,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -1205,7 +1236,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -1216,7 +1247,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -1227,7 +1258,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -1238,7 +1269,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
@@ -1249,7 +1280,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>1</v>
       </c>
@@ -1260,7 +1291,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
@@ -1271,7 +1302,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>23</v>
       </c>
@@ -1282,7 +1313,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -1293,7 +1324,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>25</v>
       </c>
@@ -1304,7 +1335,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
@@ -1315,7 +1346,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
@@ -1326,7 +1357,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
@@ -1337,7 +1368,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -1348,7 +1379,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
@@ -1359,7 +1390,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
@@ -1370,7 +1401,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -1381,7 +1412,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>33</v>
       </c>
@@ -1392,7 +1423,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
@@ -1403,7 +1434,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>35</v>
       </c>
@@ -1414,7 +1445,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
@@ -1425,7 +1456,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>37</v>
       </c>
@@ -1436,7 +1467,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>38</v>
       </c>
@@ -1447,7 +1478,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
@@ -1458,7 +1489,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>40</v>
       </c>
@@ -1469,7 +1500,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>41</v>
       </c>
@@ -1480,7 +1511,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>42</v>
       </c>
@@ -1491,7 +1522,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
@@ -1502,7 +1533,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>44</v>
       </c>
@@ -1513,7 +1544,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>45</v>
       </c>
@@ -1524,7 +1555,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>46</v>
       </c>
@@ -1535,7 +1566,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>47</v>
       </c>
@@ -1546,7 +1577,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1588,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>48</v>
       </c>
@@ -1568,7 +1599,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>49</v>
       </c>
@@ -1579,7 +1610,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>50</v>
       </c>
@@ -1590,7 +1621,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>51</v>
       </c>
@@ -1601,7 +1632,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>52</v>
       </c>
@@ -1612,7 +1643,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>53</v>
       </c>
@@ -1623,7 +1654,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>54</v>
       </c>
@@ -1634,7 +1665,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>55</v>
       </c>
@@ -1645,7 +1676,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>56</v>
       </c>
@@ -1656,7 +1687,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>57</v>
       </c>
@@ -1667,7 +1698,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>58</v>
       </c>
@@ -1678,7 +1709,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>59</v>
       </c>
@@ -1689,7 +1720,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>60</v>
       </c>
@@ -1700,7 +1731,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>61</v>
       </c>
@@ -1711,7 +1742,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>62</v>
       </c>
@@ -1722,7 +1753,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>63</v>
       </c>
@@ -1733,7 +1764,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>64</v>
       </c>
@@ -1744,7 +1775,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>65</v>
       </c>
@@ -1755,7 +1786,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>66</v>
       </c>
@@ -1766,7 +1797,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>67</v>
       </c>
@@ -1777,7 +1808,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>68</v>
       </c>
@@ -1788,7 +1819,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>69</v>
       </c>
@@ -1799,7 +1830,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>70</v>
       </c>
@@ -1810,7 +1841,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>71</v>
       </c>
@@ -1821,7 +1852,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>72</v>
       </c>
@@ -1832,7 +1863,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>73</v>
       </c>
@@ -1843,7 +1874,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>74</v>
       </c>
@@ -1854,7 +1885,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>75</v>
       </c>
@@ -1865,7 +1896,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>76</v>
       </c>
@@ -1876,7 +1907,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>77</v>
       </c>
@@ -1887,7 +1918,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>78</v>
       </c>
@@ -1898,7 +1929,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>79</v>
       </c>
@@ -1909,7 +1940,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>80</v>
       </c>
@@ -1920,7 +1951,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>81</v>
       </c>
@@ -1931,7 +1962,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>82</v>
       </c>
@@ -1942,7 +1973,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>83</v>
       </c>
@@ -1953,7 +1984,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>84</v>
       </c>
@@ -1964,7 +1995,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>85</v>
       </c>
@@ -1975,7 +2006,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>86</v>
       </c>
@@ -1986,7 +2017,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>87</v>
       </c>
@@ -1997,7 +2028,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>88</v>
       </c>
@@ -2008,7 +2039,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>89</v>
       </c>
@@ -2019,7 +2050,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>90</v>
       </c>
@@ -2030,7 +2061,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>91</v>
       </c>
@@ -2041,7 +2072,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>92</v>
       </c>
@@ -2052,7 +2083,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>93</v>
       </c>
@@ -2063,7 +2094,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>94</v>
       </c>
@@ -2074,7 +2105,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>95</v>
       </c>
@@ -2085,7 +2116,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>96</v>
       </c>
@@ -2096,7 +2127,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>97</v>
       </c>
@@ -2107,7 +2138,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>98</v>
       </c>
@@ -2118,7 +2149,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>99</v>
       </c>
@@ -2129,7 +2160,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>100</v>
       </c>
@@ -2140,7 +2171,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>101</v>
       </c>
@@ -2151,7 +2182,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>102</v>
       </c>
@@ -2162,7 +2193,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>1</v>
       </c>
@@ -2173,7 +2204,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>103</v>
       </c>
@@ -2184,7 +2215,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>104</v>
       </c>
@@ -2195,7 +2226,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>105</v>
       </c>
@@ -2206,7 +2237,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>106</v>
       </c>
@@ -2217,7 +2248,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>107</v>
       </c>
@@ -2228,7 +2259,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>108</v>
       </c>
@@ -2239,7 +2270,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>109</v>
       </c>
@@ -2250,7 +2281,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>1</v>
       </c>
@@ -2261,7 +2292,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>110</v>
       </c>
@@ -2272,7 +2303,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>1</v>
       </c>
@@ -2283,7 +2314,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>111</v>
       </c>
@@ -2294,7 +2325,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>1</v>
       </c>
@@ -2305,7 +2336,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>112</v>
       </c>
@@ -2316,7 +2347,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>1</v>
       </c>
@@ -2327,7 +2358,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>113</v>
       </c>
@@ -2338,7 +2369,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>1</v>
       </c>
@@ -2349,7 +2380,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>114</v>
       </c>
@@ -2360,7 +2391,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>115</v>
       </c>
@@ -2371,7 +2402,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>1</v>
       </c>
@@ -2382,7 +2413,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>116</v>
       </c>
@@ -2393,7 +2424,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>117</v>
       </c>
@@ -2404,7 +2435,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>120</v>
       </c>
@@ -2415,7 +2446,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>3</v>
       </c>
@@ -2426,7 +2457,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>4</v>
       </c>
@@ -2437,7 +2468,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>5</v>
       </c>
@@ -2448,7 +2479,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>6</v>
       </c>
@@ -2459,7 +2490,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>7</v>
       </c>
@@ -2470,7 +2501,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>8</v>
       </c>
@@ -2481,7 +2512,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>9</v>
       </c>
@@ -2492,7 +2523,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>10</v>
       </c>
@@ -2503,7 +2534,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>11</v>
       </c>
@@ -2514,7 +2545,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>2</v>
       </c>
@@ -2525,7 +2556,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>1</v>
       </c>
@@ -2536,7 +2567,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>121</v>
       </c>
@@ -2547,7 +2578,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>12</v>
       </c>
@@ -2558,7 +2589,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>13</v>
       </c>
@@ -2569,7 +2600,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>14</v>
       </c>
@@ -2580,7 +2611,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>15</v>
       </c>
@@ -2591,7 +2622,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>16</v>
       </c>
@@ -2602,7 +2633,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>17</v>
       </c>
@@ -2613,7 +2644,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>18</v>
       </c>
@@ -2624,7 +2655,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>19</v>
       </c>
@@ -2635,7 +2666,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>21</v>
       </c>
@@ -2646,7 +2677,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>20</v>
       </c>
@@ -2657,7 +2688,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>1</v>
       </c>
@@ -2668,7 +2699,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
         <v>22</v>
       </c>
@@ -2679,7 +2710,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
         <v>23</v>
       </c>
@@ -2690,7 +2721,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
         <v>122</v>
       </c>
@@ -2701,7 +2732,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
         <v>24</v>
       </c>
@@ -2712,7 +2743,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
         <v>25</v>
       </c>
@@ -2723,7 +2754,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
         <v>26</v>
       </c>
@@ -2734,7 +2765,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
         <v>123</v>
       </c>
@@ -2745,7 +2776,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
         <v>27</v>
       </c>
@@ -2756,7 +2787,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>124</v>
       </c>
@@ -2767,7 +2798,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>125</v>
       </c>
@@ -2778,7 +2809,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
         <v>126</v>
       </c>
@@ -2789,7 +2820,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
         <v>127</v>
       </c>
@@ -2800,7 +2831,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
         <v>128</v>
       </c>
@@ -2811,7 +2842,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
         <v>28</v>
       </c>
@@ -2822,7 +2853,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>29</v>
       </c>
@@ -2833,7 +2864,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>30</v>
       </c>
@@ -2844,7 +2875,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>31</v>
       </c>
@@ -2855,7 +2886,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
         <v>129</v>
       </c>
@@ -2866,7 +2897,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>32</v>
       </c>
@@ -2877,7 +2908,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
         <v>33</v>
       </c>
@@ -2888,7 +2919,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
         <v>34</v>
       </c>
@@ -2899,7 +2930,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
         <v>130</v>
       </c>
@@ -2910,7 +2941,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>131</v>
       </c>
@@ -2921,7 +2952,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>35</v>
       </c>
@@ -2932,7 +2963,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
         <v>36</v>
       </c>
@@ -2943,7 +2974,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
         <v>37</v>
       </c>
@@ -2954,7 +2985,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
         <v>18</v>
       </c>
@@ -2965,7 +2996,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
         <v>38</v>
       </c>
@@ -2976,7 +3007,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
         <v>132</v>
       </c>
@@ -2987,7 +3018,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>39</v>
       </c>
@@ -2998,7 +3029,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
         <v>133</v>
       </c>
@@ -3009,7 +3040,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
         <v>40</v>
       </c>
@@ -3020,7 +3051,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
         <v>41</v>
       </c>
@@ -3031,7 +3062,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
         <v>42</v>
       </c>
@@ -3042,7 +3073,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
         <v>43</v>
       </c>
@@ -3053,7 +3084,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>46</v>
       </c>
@@ -3064,7 +3095,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
         <v>47</v>
       </c>
@@ -3075,7 +3106,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>45</v>
       </c>
@@ -3086,7 +3117,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
         <v>44</v>
       </c>
@@ -3097,7 +3128,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>1</v>
       </c>
@@ -3108,7 +3139,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
         <v>48</v>
       </c>
@@ -3119,7 +3150,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
         <v>50</v>
       </c>
@@ -3130,7 +3161,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
         <v>51</v>
       </c>
@@ -3141,7 +3172,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
         <v>52</v>
       </c>
@@ -3152,7 +3183,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
         <v>53</v>
       </c>
@@ -3163,7 +3194,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
         <v>54</v>
       </c>
@@ -3174,7 +3205,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
         <v>55</v>
       </c>
@@ -3185,7 +3216,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
         <v>56</v>
       </c>
@@ -3196,7 +3227,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="202" spans="1:3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
         <v>57</v>
       </c>
@@ -3207,7 +3238,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="203" spans="1:3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
         <v>58</v>
       </c>
@@ -3218,7 +3249,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="204" spans="1:3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
         <v>59</v>
       </c>
@@ -3229,7 +3260,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="205" spans="1:3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
         <v>60</v>
       </c>
@@ -3240,7 +3271,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="206" spans="1:3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
         <v>61</v>
       </c>
@@ -3251,7 +3282,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="207" spans="1:3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
         <v>62</v>
       </c>
@@ -3262,7 +3293,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="208" spans="1:3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
         <v>63</v>
       </c>
@@ -3273,7 +3304,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="209" spans="1:3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
         <v>64</v>
       </c>
@@ -3284,7 +3315,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
         <v>65</v>
       </c>
@@ -3295,7 +3326,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="211" spans="1:3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
         <v>66</v>
       </c>
@@ -3306,7 +3337,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="212" spans="1:3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
         <v>67</v>
       </c>
@@ -3317,7 +3348,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
         <v>68</v>
       </c>
@@ -3328,7 +3359,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="6" t="s">
         <v>69</v>
       </c>
@@ -3339,7 +3370,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="6" t="s">
         <v>70</v>
       </c>
@@ -3350,7 +3381,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="216" spans="1:3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="6" t="s">
         <v>134</v>
       </c>
@@ -3361,7 +3392,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
         <v>71</v>
       </c>
@@ -3372,7 +3403,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="6" t="s">
         <v>72</v>
       </c>
@@ -3383,7 +3414,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="6" t="s">
         <v>73</v>
       </c>
@@ -3394,7 +3425,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="6" t="s">
         <v>135</v>
       </c>
@@ -3405,7 +3436,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
         <v>74</v>
       </c>
@@ -3416,7 +3447,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
         <v>75</v>
       </c>
@@ -3427,7 +3458,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
         <v>76</v>
       </c>
@@ -3438,7 +3469,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
         <v>77</v>
       </c>
@@ -3449,7 +3480,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
         <v>78</v>
       </c>
@@ -3460,7 +3491,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="226" spans="1:3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
         <v>136</v>
       </c>
@@ -3471,7 +3502,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="227" spans="1:3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
         <v>80</v>
       </c>
@@ -3482,7 +3513,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
         <v>81</v>
       </c>
@@ -3493,7 +3524,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="229" spans="1:3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
         <v>82</v>
       </c>
@@ -3504,7 +3535,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="230" spans="1:3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
         <v>83</v>
       </c>
@@ -3515,7 +3546,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="231" spans="1:3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
         <v>84</v>
       </c>
@@ -3526,7 +3557,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
         <v>85</v>
       </c>
@@ -3537,7 +3568,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
         <v>79</v>
       </c>
@@ -3548,7 +3579,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
         <v>86</v>
       </c>
@@ -3559,7 +3590,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
         <v>87</v>
       </c>
@@ -3570,7 +3601,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="236" spans="1:3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
         <v>89</v>
       </c>
@@ -3581,7 +3612,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="237" spans="1:3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
         <v>92</v>
       </c>
@@ -3592,7 +3623,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="238" spans="1:3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
         <v>90</v>
       </c>
@@ -3603,7 +3634,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
         <v>93</v>
       </c>
@@ -3614,7 +3645,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="240" spans="1:3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
         <v>95</v>
       </c>
@@ -3625,7 +3656,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
         <v>91</v>
       </c>
@@ -3636,7 +3667,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="242" spans="1:3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
         <v>96</v>
       </c>
@@ -3647,7 +3678,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="243" spans="1:3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
         <v>94</v>
       </c>
@@ -3658,7 +3689,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="244" spans="1:3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="6" t="s">
         <v>88</v>
       </c>
@@ -3669,7 +3700,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="245" spans="1:3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" s="6" t="s">
         <v>97</v>
       </c>
@@ -3680,7 +3711,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="246" spans="1:3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" s="6" t="s">
         <v>49</v>
       </c>
@@ -3691,7 +3722,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" s="6" t="s">
         <v>100</v>
       </c>
@@ -3702,7 +3733,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" s="6" t="s">
         <v>98</v>
       </c>
@@ -3713,7 +3744,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="249" spans="1:3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
         <v>99</v>
       </c>
@@ -3724,7 +3755,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
         <v>44</v>
       </c>
@@ -3735,7 +3766,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="251" spans="1:3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
         <v>101</v>
       </c>
@@ -3746,7 +3777,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="252" spans="1:3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
         <v>102</v>
       </c>
@@ -3757,7 +3788,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>1</v>
       </c>
@@ -3768,7 +3799,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" s="6" t="s">
         <v>104</v>
       </c>
@@ -3779,7 +3810,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
         <v>105</v>
       </c>
@@ -3790,7 +3821,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="256" spans="1:3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
         <v>106</v>
       </c>
@@ -3801,7 +3832,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="257" spans="1:3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
         <v>107</v>
       </c>
@@ -3812,7 +3843,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="258" spans="1:3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
         <v>108</v>
       </c>
@@ -3823,7 +3854,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
         <v>103</v>
       </c>
@@ -3834,7 +3865,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
         <v>47</v>
       </c>
@@ -3845,7 +3876,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
         <v>109</v>
       </c>
@@ -3856,7 +3887,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>1</v>
       </c>
@@ -3867,7 +3898,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
         <v>137</v>
       </c>
@@ -3878,7 +3909,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
         <v>138</v>
       </c>
@@ -3889,7 +3920,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="265" spans="1:3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
         <v>111</v>
       </c>
@@ -3900,7 +3931,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="266" spans="1:3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>1</v>
       </c>
@@ -3911,7 +3942,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="267" spans="1:3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
         <v>115</v>
       </c>
@@ -3922,7 +3953,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
         <v>114</v>
       </c>
@@ -3933,7 +3964,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>1</v>
       </c>
@@ -3944,7 +3975,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="270" spans="1:3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
         <v>113</v>
       </c>
@@ -3955,7 +3986,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="271" spans="1:3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
         <v>110</v>
       </c>
@@ -3966,7 +3997,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="272" spans="1:3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>1</v>
       </c>
@@ -3977,7 +4008,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
         <v>112</v>
       </c>
@@ -3988,7 +4019,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="274" spans="1:3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
         <v>1</v>
       </c>
@@ -3999,7 +4030,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
         <v>117</v>
       </c>
@@ -4010,7 +4041,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
         <v>116</v>
       </c>
@@ -4021,7 +4052,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="277" spans="1:3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
         <v>1</v>
       </c>
@@ -4032,7 +4063,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
         <v>113</v>
       </c>
@@ -4043,7 +4074,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1</v>
       </c>
@@ -4054,7 +4085,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>121</v>
       </c>
@@ -4065,7 +4096,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>12</v>
       </c>
@@ -4076,7 +4107,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>13</v>
       </c>
@@ -4087,7 +4118,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>20</v>
       </c>
@@ -4098,7 +4129,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>21</v>
       </c>
@@ -4109,7 +4140,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>14</v>
       </c>
@@ -4120,7 +4151,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>15</v>
       </c>
@@ -4131,7 +4162,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -4142,7 +4173,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>17</v>
       </c>
@@ -4153,7 +4184,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="289" spans="1:3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>19</v>
       </c>
@@ -4164,7 +4195,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="290" spans="1:3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1</v>
       </c>
@@ -4175,7 +4206,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="291" spans="1:3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>113</v>
       </c>
@@ -4186,7 +4217,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1</v>
       </c>
@@ -4197,7 +4228,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="293" spans="1:3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>111</v>
       </c>
@@ -4208,7 +4239,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="294" spans="1:3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>138</v>
       </c>
@@ -4219,7 +4250,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="295" spans="1:3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>137</v>
       </c>
@@ -4230,7 +4261,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="296" spans="1:3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1</v>
       </c>
@@ -4241,7 +4272,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>2</v>
       </c>
@@ -4252,7 +4283,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>120</v>
       </c>
@@ -4263,7 +4294,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>3</v>
       </c>
@@ -4274,7 +4305,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="300" spans="1:3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>4</v>
       </c>
@@ -4285,7 +4316,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="301" spans="1:3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>5</v>
       </c>
@@ -4296,7 +4327,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>7</v>
       </c>
@@ -4307,7 +4338,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>9</v>
       </c>
@@ -4318,7 +4349,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="304" spans="1:3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>10</v>
       </c>
@@ -4329,7 +4360,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>11</v>
       </c>
@@ -4340,7 +4371,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1</v>
       </c>
@@ -4351,7 +4382,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>112</v>
       </c>
@@ -4362,7 +4393,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="308" spans="1:3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1</v>
       </c>
@@ -4373,7 +4404,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="309" spans="1:3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>87</v>
       </c>
@@ -4384,7 +4415,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="310" spans="1:3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1</v>
       </c>
@@ -4395,7 +4426,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>114</v>
       </c>
@@ -4406,7 +4437,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="312" spans="1:3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1</v>
       </c>
@@ -4417,7 +4448,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="313" spans="1:3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>117</v>
       </c>
@@ -4428,7 +4459,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1</v>
       </c>
@@ -4439,7 +4470,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="315" spans="1:3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>22</v>
       </c>
@@ -4450,7 +4481,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="316" spans="1:3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>23</v>
       </c>
@@ -4461,7 +4492,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="317" spans="1:3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>122</v>
       </c>
@@ -4472,7 +4503,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="318" spans="1:3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>24</v>
       </c>
@@ -4483,7 +4514,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="319" spans="1:3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>25</v>
       </c>
@@ -4494,7 +4525,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="320" spans="1:3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>123</v>
       </c>
@@ -4505,7 +4536,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>27</v>
       </c>
@@ -4516,7 +4547,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>124</v>
       </c>
@@ -4527,7 +4558,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="323" spans="1:3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>125</v>
       </c>
@@ -4538,7 +4569,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>126</v>
       </c>
@@ -4549,7 +4580,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>139</v>
       </c>
@@ -4560,7 +4591,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>128</v>
       </c>
@@ -4571,7 +4602,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>140</v>
       </c>
@@ -4582,7 +4613,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="328" spans="1:3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>129</v>
       </c>
@@ -4593,7 +4624,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="329" spans="1:3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>32</v>
       </c>
@@ -4604,7 +4635,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>34</v>
       </c>
@@ -4615,7 +4646,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="331" spans="1:3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>130</v>
       </c>
@@ -4626,7 +4657,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>131</v>
       </c>
@@ -4637,7 +4668,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="333" spans="1:3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>35</v>
       </c>
@@ -4648,7 +4679,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="334" spans="1:3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>36</v>
       </c>
@@ -4659,7 +4690,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>43</v>
       </c>
@@ -4670,7 +4701,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="336" spans="1:3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>38</v>
       </c>
@@ -4681,7 +4712,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>132</v>
       </c>
@@ -4692,7 +4723,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>39</v>
       </c>
@@ -4703,7 +4734,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>46</v>
       </c>
@@ -4714,7 +4745,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -4725,7 +4756,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>141</v>
       </c>
@@ -4736,7 +4767,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>142</v>
       </c>
@@ -4747,7 +4778,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="343" spans="1:3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>41</v>
       </c>
@@ -4758,7 +4789,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>42</v>
       </c>
@@ -4769,7 +4800,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>18</v>
       </c>
@@ -4780,7 +4811,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>133</v>
       </c>
@@ -4791,7 +4822,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1</v>
       </c>
@@ -4802,7 +4833,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="348" spans="1:3">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>103</v>
       </c>
@@ -4813,7 +4844,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="349" spans="1:3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>109</v>
       </c>
@@ -4824,7 +4855,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>104</v>
       </c>
@@ -4835,7 +4866,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="351" spans="1:3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>47</v>
       </c>
@@ -4846,7 +4877,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>106</v>
       </c>
@@ -4857,7 +4888,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="353" spans="1:3">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>107</v>
       </c>
@@ -4868,7 +4899,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="354" spans="1:3">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>108</v>
       </c>
@@ -4879,7 +4910,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="355" spans="1:3">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1</v>
       </c>
@@ -4890,7 +4921,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="356" spans="1:3">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>86</v>
       </c>
@@ -4901,7 +4932,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="357" spans="1:3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>48</v>
       </c>
@@ -4912,7 +4943,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="358" spans="1:3">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>143</v>
       </c>
@@ -4923,7 +4954,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="359" spans="1:3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>50</v>
       </c>
@@ -4934,7 +4965,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="360" spans="1:3">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>144</v>
       </c>
@@ -4945,7 +4976,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="361" spans="1:3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>51</v>
       </c>
@@ -4956,7 +4987,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="362" spans="1:3">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>52</v>
       </c>
@@ -4967,7 +4998,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="363" spans="1:3">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>53</v>
       </c>
@@ -4978,7 +5009,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="364" spans="1:3">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>145</v>
       </c>
@@ -4989,7 +5020,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="365" spans="1:3">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>146</v>
       </c>
@@ -5000,7 +5031,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="366" spans="1:3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>57</v>
       </c>
@@ -5011,7 +5042,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>92</v>
       </c>
@@ -5022,7 +5053,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="368" spans="1:3">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>59</v>
       </c>
@@ -5033,7 +5064,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="369" spans="1:3">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>60</v>
       </c>
@@ -5044,7 +5075,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="370" spans="1:3">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>62</v>
       </c>
@@ -5055,7 +5086,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="371" spans="1:3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>63</v>
       </c>
@@ -5066,7 +5097,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="372" spans="1:3">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>64</v>
       </c>
@@ -5077,7 +5108,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="373" spans="1:3">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>66</v>
       </c>
@@ -5088,7 +5119,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="374" spans="1:3">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>67</v>
       </c>
@@ -5099,7 +5130,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="375" spans="1:3">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>147</v>
       </c>
@@ -5110,7 +5141,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="376" spans="1:3">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>89</v>
       </c>
@@ -5121,7 +5152,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="377" spans="1:3">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>94</v>
       </c>
@@ -5132,7 +5163,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="378" spans="1:3">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>70</v>
       </c>
@@ -5143,7 +5174,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="379" spans="1:3">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>134</v>
       </c>
@@ -5154,7 +5185,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="380" spans="1:3">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>90</v>
       </c>
@@ -5165,7 +5196,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="381" spans="1:3">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>71</v>
       </c>
@@ -5176,7 +5207,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="382" spans="1:3">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>73</v>
       </c>
@@ -5187,7 +5218,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="383" spans="1:3">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>87</v>
       </c>
@@ -5198,7 +5229,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="384" spans="1:3">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>135</v>
       </c>
@@ -5209,7 +5240,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="385" spans="1:3">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>74</v>
       </c>
@@ -5220,7 +5251,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="386" spans="1:3">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>76</v>
       </c>
@@ -5231,7 +5262,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="387" spans="1:3">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>148</v>
       </c>
@@ -5242,7 +5273,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="388" spans="1:3">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>98</v>
       </c>
@@ -5253,7 +5284,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="389" spans="1:3">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>99</v>
       </c>
@@ -5264,7 +5295,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="390" spans="1:3">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>149</v>
       </c>
@@ -5275,7 +5306,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="391" spans="1:3">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>102</v>
       </c>
@@ -5286,7 +5317,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="392" spans="1:3">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>79</v>
       </c>
@@ -5297,7 +5328,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="393" spans="1:3">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>150</v>
       </c>
@@ -5308,7 +5339,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="394" spans="1:3">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>136</v>
       </c>
@@ -5319,7 +5350,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="395" spans="1:3">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>82</v>
       </c>
@@ -5330,7 +5361,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="396" spans="1:3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>83</v>
       </c>
@@ -5341,7 +5372,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="397" spans="1:3">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>88</v>
       </c>
@@ -5352,7 +5383,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="398" spans="1:3">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>93</v>
       </c>
@@ -5363,7 +5394,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="399" spans="1:3">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>95</v>
       </c>
@@ -5374,7 +5405,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="400" spans="1:3">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>96</v>
       </c>
@@ -5385,7 +5416,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="401" spans="1:3">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>151</v>
       </c>
@@ -5396,7 +5427,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="402" spans="1:3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>97</v>
       </c>
@@ -5407,7 +5438,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>44</v>
       </c>
@@ -5418,7 +5449,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="404" spans="1:3">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>85</v>
       </c>
@@ -5429,7 +5460,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>100</v>
       </c>
@@ -5440,7 +5471,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="406" spans="1:3">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>69</v>
       </c>
@@ -5451,7 +5482,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="407" spans="1:3">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>49</v>
       </c>
@@ -5462,7 +5493,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="408" spans="1:3">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>84</v>
       </c>
@@ -5473,7 +5504,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="409" spans="1:3">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
         <v>113</v>
       </c>
@@ -5484,7 +5515,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
         <v>1</v>
       </c>
@@ -5495,7 +5526,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="411" spans="1:3">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
         <v>7</v>
       </c>
@@ -5506,7 +5537,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="412" spans="1:3">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
         <v>152</v>
       </c>
@@ -5517,7 +5548,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="413" spans="1:3">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
         <v>9</v>
       </c>
@@ -5528,7 +5559,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="414" spans="1:3">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
         <v>11</v>
       </c>
@@ -5539,7 +5570,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="415" spans="1:3">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" s="6" t="s">
         <v>4</v>
       </c>
@@ -5550,7 +5581,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="416" spans="1:3">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" s="6" t="s">
         <v>3</v>
       </c>
@@ -5561,7 +5592,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="417" spans="1:3">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" s="6" t="s">
         <v>10</v>
       </c>
@@ -5572,7 +5603,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="418" spans="1:3">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" s="6" t="s">
         <v>2</v>
       </c>
@@ -5583,7 +5614,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="419" spans="1:3">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" s="6" t="s">
         <v>5</v>
       </c>
@@ -5594,7 +5625,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="420" spans="1:3">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
         <v>1</v>
       </c>
@@ -5605,7 +5636,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="421" spans="1:3">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
         <v>15</v>
       </c>
@@ -5616,7 +5647,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="422" spans="1:3">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5658,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="423" spans="1:3">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
         <v>12</v>
       </c>
@@ -5638,7 +5669,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="424" spans="1:3">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
         <v>20</v>
       </c>
@@ -5649,7 +5680,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="425" spans="1:3">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
         <v>21</v>
       </c>
@@ -5660,7 +5691,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="426" spans="1:3">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
         <v>16</v>
       </c>
@@ -5671,7 +5702,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="427" spans="1:3">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
         <v>14</v>
       </c>
@@ -5682,7 +5713,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="428" spans="1:3">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
         <v>153</v>
       </c>
@@ -5693,7 +5724,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="429" spans="1:3">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
         <v>17</v>
       </c>
@@ -5704,7 +5735,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="430" spans="1:3">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
         <v>154</v>
       </c>
@@ -5715,7 +5746,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="431" spans="1:3">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
         <v>121</v>
       </c>
@@ -5726,7 +5757,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="432" spans="1:3">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
         <v>1</v>
       </c>
@@ -5737,7 +5768,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="433" spans="1:3">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" s="6" t="s">
         <v>155</v>
       </c>
@@ -5748,7 +5779,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="434" spans="1:3">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" s="6" t="s">
         <v>38</v>
       </c>
@@ -5759,7 +5790,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="435" spans="1:3">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" s="6" t="s">
         <v>132</v>
       </c>
@@ -5770,7 +5801,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="436" spans="1:3">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" s="6" t="s">
         <v>142</v>
       </c>
@@ -5781,7 +5812,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="437" spans="1:3">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" s="6" t="s">
         <v>130</v>
       </c>
@@ -5792,7 +5823,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="438" spans="1:3">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" s="6" t="s">
         <v>22</v>
       </c>
@@ -5803,7 +5834,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="439" spans="1:3">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
         <v>24</v>
       </c>
@@ -5814,7 +5845,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="440" spans="1:3">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
         <v>126</v>
       </c>
@@ -5825,7 +5856,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="441" spans="1:3">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
         <v>128</v>
       </c>
@@ -5836,7 +5867,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="442" spans="1:3">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
         <v>36</v>
       </c>
@@ -5847,7 +5878,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="443" spans="1:3">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
         <v>123</v>
       </c>
@@ -5858,7 +5889,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="444" spans="1:3">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" s="6" t="s">
         <v>133</v>
       </c>
@@ -5869,7 +5900,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="445" spans="1:3">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" s="6" t="s">
         <v>40</v>
       </c>
@@ -5880,7 +5911,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="446" spans="1:3">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" s="6" t="s">
         <v>139</v>
       </c>
@@ -5891,7 +5922,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="447" spans="1:3">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
         <v>46</v>
       </c>
@@ -5902,7 +5933,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="448" spans="1:3">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" s="6" t="s">
         <v>156</v>
       </c>
@@ -5913,7 +5944,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="449" spans="1:3">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" s="6" t="s">
         <v>27</v>
       </c>
@@ -5924,7 +5955,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="450" spans="1:3">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" s="6" t="s">
         <v>131</v>
       </c>
@@ -5935,7 +5966,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="451" spans="1:3">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
         <v>43</v>
       </c>
@@ -5946,7 +5977,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="452" spans="1:3">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" s="6" t="s">
         <v>35</v>
       </c>
@@ -5957,7 +5988,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="453" spans="1:3">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" s="6" t="s">
         <v>39</v>
       </c>
@@ -5968,7 +5999,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="454" spans="1:3">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" s="6" t="s">
         <v>42</v>
       </c>
@@ -5979,7 +6010,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="455" spans="1:3">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" s="6" t="s">
         <v>141</v>
       </c>
@@ -5990,7 +6021,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="456" spans="1:3">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" s="6" t="s">
         <v>140</v>
       </c>
@@ -6001,7 +6032,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="457" spans="1:3">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" s="6" t="s">
         <v>34</v>
       </c>
@@ -6012,7 +6043,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="458" spans="1:3">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
         <v>18</v>
       </c>
@@ -6023,7 +6054,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="459" spans="1:3">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" s="6" t="s">
         <v>23</v>
       </c>
@@ -6034,7 +6065,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="460" spans="1:3">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
         <v>25</v>
       </c>
@@ -6045,7 +6076,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="461" spans="1:3">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" s="6" t="s">
         <v>32</v>
       </c>
@@ -6056,7 +6087,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="462" spans="1:3">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
         <v>124</v>
       </c>
@@ -6067,7 +6098,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="463" spans="1:3">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
         <v>1</v>
       </c>
@@ -6078,7 +6109,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="464" spans="1:3">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
         <v>109</v>
       </c>
@@ -6089,7 +6120,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="465" spans="1:3">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" s="6" t="s">
         <v>108</v>
       </c>
@@ -6100,7 +6131,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="466" spans="1:3">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" s="6" t="s">
         <v>103</v>
       </c>
@@ -6111,7 +6142,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="467" spans="1:3">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" s="6" t="s">
         <v>104</v>
       </c>
@@ -6122,7 +6153,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="468" spans="1:3">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
         <v>107</v>
       </c>
@@ -6133,7 +6164,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="469" spans="1:3">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
         <v>106</v>
       </c>
@@ -6144,7 +6175,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="470" spans="1:3">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
         <v>47</v>
       </c>
@@ -6155,7 +6186,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="471" spans="1:3">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
         <v>1</v>
       </c>
@@ -6166,7 +6197,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="472" spans="1:3">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" s="6" t="s">
         <v>64</v>
       </c>
@@ -6177,7 +6208,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="473" spans="1:3">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" s="6" t="s">
         <v>94</v>
       </c>
@@ -6188,7 +6219,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="474" spans="1:3">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" s="6" t="s">
         <v>70</v>
       </c>
@@ -6199,7 +6230,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="475" spans="1:3">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" s="6" t="s">
         <v>73</v>
       </c>
@@ -6210,7 +6241,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="476" spans="1:3">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" s="6" t="s">
         <v>149</v>
       </c>
@@ -6221,7 +6252,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="477" spans="1:3">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" s="6" t="s">
         <v>82</v>
       </c>
@@ -6232,7 +6263,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="478" spans="1:3">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" s="6" t="s">
         <v>95</v>
       </c>
@@ -6243,7 +6274,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="479" spans="1:3">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" s="6" t="s">
         <v>151</v>
       </c>
@@ -6254,7 +6285,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="480" spans="1:3">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" s="6" t="s">
         <v>144</v>
       </c>
@@ -6265,7 +6296,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="481" spans="1:3">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" s="6" t="s">
         <v>146</v>
       </c>
@@ -6276,7 +6307,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="482" spans="1:3">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" s="6" t="s">
         <v>86</v>
       </c>
@@ -6287,7 +6318,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="483" spans="1:3">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" s="6" t="s">
         <v>76</v>
       </c>
@@ -6298,7 +6329,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="484" spans="1:3">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" s="6" t="s">
         <v>61</v>
       </c>
@@ -6309,7 +6340,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="485" spans="1:3">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" s="6" t="s">
         <v>63</v>
       </c>
@@ -6320,7 +6351,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="486" spans="1:3">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" s="6" t="s">
         <v>69</v>
       </c>
@@ -6331,7 +6362,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="487" spans="1:3">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" s="6" t="s">
         <v>135</v>
       </c>
@@ -6342,7 +6373,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="488" spans="1:3">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" s="6" t="s">
         <v>148</v>
       </c>
@@ -6353,7 +6384,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="489" spans="1:3">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" s="6" t="s">
         <v>83</v>
       </c>
@@ -6364,7 +6395,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="490" spans="1:3">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" s="6" t="s">
         <v>84</v>
       </c>
@@ -6375,7 +6406,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="491" spans="1:3">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" s="6" t="s">
         <v>71</v>
       </c>
@@ -6386,7 +6417,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="492" spans="1:3">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" s="6" t="s">
         <v>97</v>
       </c>
@@ -6397,7 +6428,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="493" spans="1:3">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" s="6" t="s">
         <v>90</v>
       </c>
@@ -6408,7 +6439,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="494" spans="1:3">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" s="6" t="s">
         <v>60</v>
       </c>
@@ -6419,7 +6450,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="495" spans="1:3">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" s="6" t="s">
         <v>93</v>
       </c>
@@ -6430,7 +6461,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="496" spans="1:3">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" s="6" t="s">
         <v>85</v>
       </c>
@@ -6441,7 +6472,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="497" spans="1:3">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" s="6" t="s">
         <v>53</v>
       </c>
@@ -6452,7 +6483,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="498" spans="1:3">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" s="6" t="s">
         <v>147</v>
       </c>
@@ -6463,7 +6494,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="499" spans="1:3">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" s="6" t="s">
         <v>50</v>
       </c>
@@ -6474,7 +6505,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="500" spans="1:3">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" s="6" t="s">
         <v>51</v>
       </c>
@@ -6485,7 +6516,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="501" spans="1:3">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" s="6" t="s">
         <v>52</v>
       </c>
@@ -6496,7 +6527,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="502" spans="1:3">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" s="6" t="s">
         <v>145</v>
       </c>
@@ -6507,7 +6538,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="503" spans="1:3">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" s="6" t="s">
         <v>59</v>
       </c>
@@ -6518,7 +6549,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="504" spans="1:3">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" s="6" t="s">
         <v>66</v>
       </c>
@@ -6529,7 +6560,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="505" spans="1:3">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" s="6" t="s">
         <v>49</v>
       </c>
@@ -6540,7 +6571,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="506" spans="1:3">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" s="6" t="s">
         <v>100</v>
       </c>
@@ -6551,7 +6582,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="507" spans="1:3">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507" s="6" t="s">
         <v>89</v>
       </c>
@@ -6562,7 +6593,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="508" spans="1:3">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508" s="6" t="s">
         <v>134</v>
       </c>
@@ -6573,7 +6604,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="509" spans="1:3">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" s="6" t="s">
         <v>62</v>
       </c>
@@ -6584,7 +6615,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="510" spans="1:3">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510" s="6" t="s">
         <v>44</v>
       </c>
@@ -6595,7 +6626,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="511" spans="1:3">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" s="6" t="s">
         <v>88</v>
       </c>
@@ -6606,7 +6637,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="512" spans="1:3">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" s="6" t="s">
         <v>96</v>
       </c>
@@ -6617,7 +6648,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="513" spans="1:3">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" s="6" t="s">
         <v>99</v>
       </c>
@@ -6628,7 +6659,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="514" spans="1:3">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514" s="6" t="s">
         <v>102</v>
       </c>
@@ -6639,7 +6670,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="515" spans="1:3">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515" s="6" t="s">
         <v>157</v>
       </c>
@@ -6650,7 +6681,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="516" spans="1:3">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516" s="6" t="s">
         <v>150</v>
       </c>
@@ -6661,7 +6692,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="517" spans="1:3">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" s="6" t="s">
         <v>92</v>
       </c>
@@ -6672,7 +6703,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="518" spans="1:3">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518" s="6" t="s">
         <v>79</v>
       </c>
@@ -6683,7 +6714,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="519" spans="1:3">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" s="6" t="s">
         <v>74</v>
       </c>
@@ -6694,7 +6725,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="520" spans="1:3">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" s="6" t="s">
         <v>98</v>
       </c>
@@ -6705,7 +6736,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="521" spans="1:3">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" s="6" t="s">
         <v>48</v>
       </c>
@@ -6716,7 +6747,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="522" spans="1:3">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" s="6" t="s">
         <v>57</v>
       </c>
@@ -6727,7 +6758,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="523" spans="1:3">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" s="6" t="s">
         <v>77</v>
       </c>
@@ -6738,7 +6769,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="524" spans="1:3">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" s="3" t="s">
         <v>1</v>
       </c>
@@ -6749,7 +6780,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="525" spans="1:3">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" s="6" t="s">
         <v>111</v>
       </c>
@@ -6760,7 +6791,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="526" spans="1:3">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" s="6" t="s">
         <v>138</v>
       </c>
@@ -6771,7 +6802,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="527" spans="1:3">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" s="6" t="s">
         <v>137</v>
       </c>
@@ -6782,7 +6813,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="528" spans="1:3">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A528" s="3" t="s">
         <v>1</v>
       </c>
@@ -6793,7 +6824,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="529" spans="1:3">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A529" s="6" t="s">
         <v>117</v>
       </c>
@@ -6804,7 +6835,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="530" spans="1:3">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A530" s="3" t="s">
         <v>1</v>
       </c>
@@ -6815,7 +6846,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="531" spans="1:3">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531" s="6" t="s">
         <v>112</v>
       </c>
@@ -6826,7 +6857,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="532" spans="1:3">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A532" s="3" t="s">
         <v>1</v>
       </c>
@@ -6837,7 +6868,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="533" spans="1:3">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A533" s="6" t="s">
         <v>114</v>
       </c>
@@ -6848,7 +6879,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="534" spans="1:3">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A534" s="11" t="s">
         <v>1</v>
       </c>
@@ -6859,7 +6890,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="535" spans="1:3">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A535" s="10" t="s">
         <v>121</v>
       </c>
@@ -6870,7 +6901,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="536" spans="1:3">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A536" s="10" t="s">
         <v>12</v>
       </c>
@@ -6881,7 +6912,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="537" spans="1:3">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A537" s="10" t="s">
         <v>154</v>
       </c>
@@ -6892,7 +6923,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="538" spans="1:3">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A538" s="10" t="s">
         <v>20</v>
       </c>
@@ -6903,7 +6934,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="539" spans="1:3">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A539" s="10" t="s">
         <v>21</v>
       </c>
@@ -6914,7 +6945,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="540" spans="1:3">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540" s="10" t="s">
         <v>14</v>
       </c>
@@ -6925,7 +6956,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="541" spans="1:3">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A541" s="10" t="s">
         <v>15</v>
       </c>
@@ -6936,7 +6967,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="542" spans="1:3">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A542" s="10" t="s">
         <v>16</v>
       </c>
@@ -6947,7 +6978,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="543" spans="1:3">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A543" s="10" t="s">
         <v>17</v>
       </c>
@@ -6958,7 +6989,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="544" spans="1:3">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A544" s="10" t="s">
         <v>153</v>
       </c>
@@ -6969,7 +7000,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="545" spans="1:3">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A545" s="10" t="s">
         <v>19</v>
       </c>
@@ -6980,7 +7011,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="546" spans="1:3">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546" s="11" t="s">
         <v>1</v>
       </c>
@@ -6991,7 +7022,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="547" spans="1:3">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A547" s="10" t="s">
         <v>113</v>
       </c>
@@ -7002,7 +7033,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="548" spans="1:3">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A548" s="11" t="s">
         <v>1</v>
       </c>
@@ -7013,7 +7044,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="549" spans="1:3">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A549" s="10" t="s">
         <v>111</v>
       </c>
@@ -7024,7 +7055,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="550" spans="1:3">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A550" s="10" t="s">
         <v>138</v>
       </c>
@@ -7035,7 +7066,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="551" spans="1:3">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A551" s="10" t="s">
         <v>137</v>
       </c>
@@ -7046,7 +7077,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="552" spans="1:3">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A552" s="11" t="s">
         <v>1</v>
       </c>
@@ -7057,7 +7088,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="553" spans="1:3">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A553" s="10" t="s">
         <v>158</v>
       </c>
@@ -7068,7 +7099,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="554" spans="1:3">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554" s="11" t="s">
         <v>1</v>
       </c>
@@ -7079,7 +7110,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="555" spans="1:3">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555" s="10" t="s">
         <v>2</v>
       </c>
@@ -7090,7 +7121,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="556" spans="1:3">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556" s="10" t="s">
         <v>3</v>
       </c>
@@ -7101,7 +7132,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="557" spans="1:3">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A557" s="10" t="s">
         <v>4</v>
       </c>
@@ -7112,7 +7143,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="558" spans="1:3">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A558" s="10" t="s">
         <v>5</v>
       </c>
@@ -7123,7 +7154,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="559" spans="1:3">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A559" s="10" t="s">
         <v>7</v>
       </c>
@@ -7134,7 +7165,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="560" spans="1:3">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A560" s="10" t="s">
         <v>152</v>
       </c>
@@ -7145,7 +7176,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="561" spans="1:3">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561" s="10" t="s">
         <v>9</v>
       </c>
@@ -7156,7 +7187,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="562" spans="1:3">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A562" s="10" t="s">
         <v>10</v>
       </c>
@@ -7167,7 +7198,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="563" spans="1:3">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A563" s="10" t="s">
         <v>11</v>
       </c>
@@ -7178,7 +7209,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="564" spans="1:3">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A564" s="11" t="s">
         <v>1</v>
       </c>
@@ -7189,7 +7220,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="565" spans="1:3">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565" s="10" t="s">
         <v>112</v>
       </c>
@@ -7200,7 +7231,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="566" spans="1:3">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A566" s="11" t="s">
         <v>1</v>
       </c>
@@ -7211,7 +7242,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="567" spans="1:3">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A567" s="10" t="s">
         <v>117</v>
       </c>
@@ -7222,7 +7253,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="568" spans="1:3">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A568" s="11" t="s">
         <v>1</v>
       </c>
@@ -7233,7 +7264,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="569" spans="1:3">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A569" s="10" t="s">
         <v>159</v>
       </c>
@@ -7244,7 +7275,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="570" spans="1:3">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A570" s="10" t="s">
         <v>22</v>
       </c>
@@ -7255,7 +7286,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="571" spans="1:3">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A571" s="10" t="s">
         <v>23</v>
       </c>
@@ -7266,7 +7297,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="572" spans="1:3">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A572" s="10" t="s">
         <v>160</v>
       </c>
@@ -7277,7 +7308,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="573" spans="1:3">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A573" s="10" t="s">
         <v>24</v>
       </c>
@@ -7288,7 +7319,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="574" spans="1:3">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A574" s="10" t="s">
         <v>123</v>
       </c>
@@ -7299,7 +7330,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="575" spans="1:3">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A575" s="10" t="s">
         <v>27</v>
       </c>
@@ -7310,7 +7341,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="576" spans="1:3">
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A576" s="10" t="s">
         <v>161</v>
       </c>
@@ -7321,7 +7352,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="577" spans="1:3">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A577" s="10" t="s">
         <v>162</v>
       </c>
@@ -7332,7 +7363,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="578" spans="1:3">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A578" s="10" t="s">
         <v>163</v>
       </c>
@@ -7343,7 +7374,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="579" spans="1:3">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A579" s="10" t="s">
         <v>139</v>
       </c>
@@ -7354,7 +7385,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="580" spans="1:3">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A580" s="10" t="s">
         <v>164</v>
       </c>
@@ -7365,7 +7396,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="581" spans="1:3">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A581" s="10" t="s">
         <v>165</v>
       </c>
@@ -7376,7 +7407,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="582" spans="1:3">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A582" s="10" t="s">
         <v>166</v>
       </c>
@@ -7387,7 +7418,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="583" spans="1:3">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583" s="10" t="s">
         <v>128</v>
       </c>
@@ -7398,7 +7429,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="584" spans="1:3">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A584" s="10" t="s">
         <v>167</v>
       </c>
@@ -7409,7 +7440,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="585" spans="1:3">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A585" s="10" t="s">
         <v>168</v>
       </c>
@@ -7420,7 +7451,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="586" spans="1:3">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A586" s="10" t="s">
         <v>140</v>
       </c>
@@ -7431,7 +7462,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="587" spans="1:3">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A587" s="10" t="s">
         <v>156</v>
       </c>
@@ -7442,7 +7473,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="588" spans="1:3">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588" s="10" t="s">
         <v>169</v>
       </c>
@@ -7453,7 +7484,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="589" spans="1:3">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589" s="10" t="s">
         <v>34</v>
       </c>
@@ -7464,7 +7495,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="590" spans="1:3">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" s="10" t="s">
         <v>130</v>
       </c>
@@ -7475,7 +7506,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="591" spans="1:3">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A591" s="10" t="s">
         <v>131</v>
       </c>
@@ -7486,7 +7517,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="592" spans="1:3">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A592" s="10" t="s">
         <v>35</v>
       </c>
@@ -7497,7 +7528,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="593" spans="1:3">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593" s="10" t="s">
         <v>36</v>
       </c>
@@ -7508,7 +7539,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="594" spans="1:3">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594" s="10" t="s">
         <v>43</v>
       </c>
@@ -7519,7 +7550,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="595" spans="1:3">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595" s="10" t="s">
         <v>170</v>
       </c>
@@ -7530,7 +7561,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="596" spans="1:3">
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596" s="10" t="s">
         <v>18</v>
       </c>
@@ -7541,7 +7572,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="597" spans="1:3">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597" s="10" t="s">
         <v>132</v>
       </c>
@@ -7552,7 +7583,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="598" spans="1:3">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598" s="10" t="s">
         <v>171</v>
       </c>
@@ -7563,7 +7594,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="599" spans="1:3">
+    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599" s="10" t="s">
         <v>39</v>
       </c>
@@ -7574,7 +7605,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="600" spans="1:3">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A600" s="10" t="s">
         <v>133</v>
       </c>
@@ -7585,7 +7616,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="601" spans="1:3">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601" s="10" t="s">
         <v>172</v>
       </c>
@@ -7596,7 +7627,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="602" spans="1:3">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602" s="10" t="s">
         <v>46</v>
       </c>
@@ -7607,7 +7638,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="603" spans="1:3">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A603" s="10" t="s">
         <v>40</v>
       </c>
@@ -7618,7 +7649,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="604" spans="1:3">
+    <row r="604" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A604" s="10" t="s">
         <v>173</v>
       </c>
@@ -7629,7 +7660,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="605" spans="1:3">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605" s="10" t="s">
         <v>141</v>
       </c>
@@ -7640,7 +7671,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="606" spans="1:3">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A606" s="10" t="s">
         <v>142</v>
       </c>
@@ -7651,7 +7682,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="607" spans="1:3">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607" s="10" t="s">
         <v>126</v>
       </c>
@@ -7662,7 +7693,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="608" spans="1:3">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608" s="11" t="s">
         <v>1</v>
       </c>
@@ -7673,7 +7704,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="609" spans="1:3">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A609" s="10" t="s">
         <v>174</v>
       </c>
@@ -7684,7 +7715,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="610" spans="1:3">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" s="10" t="s">
         <v>86</v>
       </c>
@@ -7695,7 +7726,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="611" spans="1:3">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A611" s="10" t="s">
         <v>175</v>
       </c>
@@ -7706,7 +7737,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="612" spans="1:3">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A612" s="10" t="s">
         <v>48</v>
       </c>
@@ -7717,7 +7748,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="613" spans="1:3">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" s="10" t="s">
         <v>50</v>
       </c>
@@ -7728,7 +7759,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="614" spans="1:3">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614" s="10" t="s">
         <v>144</v>
       </c>
@@ -7739,7 +7770,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="615" spans="1:3">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A615" s="10" t="s">
         <v>176</v>
       </c>
@@ -7750,7 +7781,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="616" spans="1:3">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616" s="10" t="s">
         <v>51</v>
       </c>
@@ -7761,7 +7792,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="617" spans="1:3">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A617" s="10" t="s">
         <v>52</v>
       </c>
@@ -7772,7 +7803,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="618" spans="1:3">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618" s="10" t="s">
         <v>53</v>
       </c>
@@ -7783,7 +7814,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="619" spans="1:3">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619" s="10" t="s">
         <v>145</v>
       </c>
@@ -7794,7 +7825,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="620" spans="1:3">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620" s="10" t="s">
         <v>146</v>
       </c>
@@ -7805,7 +7836,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="621" spans="1:3">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621" s="10" t="s">
         <v>92</v>
       </c>
@@ -7816,7 +7847,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="622" spans="1:3">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622" s="10" t="s">
         <v>59</v>
       </c>
@@ -7827,7 +7858,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="623" spans="1:3">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A623" s="10" t="s">
         <v>61</v>
       </c>
@@ -7838,7 +7869,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="624" spans="1:3">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624" s="10" t="s">
         <v>62</v>
       </c>
@@ -7849,7 +7880,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="625" spans="1:3">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A625" s="10" t="s">
         <v>177</v>
       </c>
@@ -7860,7 +7891,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="626" spans="1:3">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626" s="10" t="s">
         <v>63</v>
       </c>
@@ -7871,7 +7902,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="627" spans="1:3">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627" s="10" t="s">
         <v>157</v>
       </c>
@@ -7882,7 +7913,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="628" spans="1:3">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A628" s="10" t="s">
         <v>66</v>
       </c>
@@ -7893,7 +7924,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="629" spans="1:3">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629" s="10" t="s">
         <v>147</v>
       </c>
@@ -7904,7 +7935,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="630" spans="1:3">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630" s="10" t="s">
         <v>89</v>
       </c>
@@ -7915,7 +7946,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="631" spans="1:3">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631" s="10" t="s">
         <v>70</v>
       </c>
@@ -7926,7 +7957,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="632" spans="1:3">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632" s="10" t="s">
         <v>178</v>
       </c>
@@ -7937,7 +7968,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="633" spans="1:3">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" s="10" t="s">
         <v>134</v>
       </c>
@@ -7948,7 +7979,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="634" spans="1:3">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" s="10" t="s">
         <v>90</v>
       </c>
@@ -7959,7 +7990,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="635" spans="1:3">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A635" s="10" t="s">
         <v>71</v>
       </c>
@@ -7970,7 +8001,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="636" spans="1:3">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636" s="10" t="s">
         <v>135</v>
       </c>
@@ -7981,7 +8012,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="637" spans="1:3">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637" s="10" t="s">
         <v>74</v>
       </c>
@@ -7992,7 +8023,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="638" spans="1:3">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638" s="10" t="s">
         <v>76</v>
       </c>
@@ -8003,7 +8034,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="639" spans="1:3">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A639" s="10" t="s">
         <v>179</v>
       </c>
@@ -8014,7 +8045,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="640" spans="1:3">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A640" s="10" t="s">
         <v>98</v>
       </c>
@@ -8025,7 +8056,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="641" spans="1:3">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641" s="10" t="s">
         <v>180</v>
       </c>
@@ -8036,7 +8067,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="642" spans="1:3">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642" s="10" t="s">
         <v>102</v>
       </c>
@@ -8047,7 +8078,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="643" spans="1:3">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643" s="10" t="s">
         <v>136</v>
       </c>
@@ -8058,7 +8089,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="644" spans="1:3">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644" s="10" t="s">
         <v>181</v>
       </c>
@@ -8069,7 +8100,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="645" spans="1:3">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" s="10" t="s">
         <v>83</v>
       </c>
@@ -8080,7 +8111,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="646" spans="1:3">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646" s="10" t="s">
         <v>84</v>
       </c>
@@ -8091,7 +8122,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="647" spans="1:3">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" s="10" t="s">
         <v>182</v>
       </c>
@@ -8102,7 +8133,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="648" spans="1:3">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648" s="10" t="s">
         <v>85</v>
       </c>
@@ -8113,7 +8144,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="649" spans="1:3">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649" s="10" t="s">
         <v>96</v>
       </c>
@@ -8124,7 +8155,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="650" spans="1:3">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A650" s="10" t="s">
         <v>183</v>
       </c>
@@ -8135,7 +8166,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="651" spans="1:3">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A651" s="10" t="s">
         <v>184</v>
       </c>
@@ -8146,7 +8177,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="652" spans="1:3">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A652" s="10" t="s">
         <v>151</v>
       </c>
@@ -8157,7 +8188,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="653" spans="1:3">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A653" s="10" t="s">
         <v>97</v>
       </c>
@@ -8168,7 +8199,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="654" spans="1:3">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A654" s="10" t="s">
         <v>64</v>
       </c>
@@ -8179,7 +8210,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="655" spans="1:3">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A655" s="10" t="s">
         <v>69</v>
       </c>
@@ -8190,7 +8221,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="656" spans="1:3">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A656" s="10" t="s">
         <v>148</v>
       </c>
@@ -8201,7 +8232,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="657" spans="1:3">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A657" s="10" t="s">
         <v>88</v>
       </c>
@@ -8212,7 +8243,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="658" spans="1:3">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A658" s="10" t="s">
         <v>49</v>
       </c>
@@ -8223,7 +8254,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="659" spans="1:3">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A659" s="10" t="s">
         <v>100</v>
       </c>
@@ -8234,7 +8265,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="660" spans="1:3">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A660" s="10" t="s">
         <v>44</v>
       </c>
@@ -8245,7 +8276,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="661" spans="1:3">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A661" s="11" t="s">
         <v>1</v>
       </c>
@@ -8256,7 +8287,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="662" spans="1:3">
+    <row r="662" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A662" s="10" t="s">
         <v>103</v>
       </c>
@@ -8267,7 +8298,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="663" spans="1:3">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A663" s="10" t="s">
         <v>109</v>
       </c>
@@ -8278,7 +8309,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="664" spans="1:3">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A664" s="10" t="s">
         <v>104</v>
       </c>
@@ -8289,7 +8320,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="665" spans="1:3">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A665" s="10" t="s">
         <v>106</v>
       </c>
@@ -8300,7 +8331,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="666" spans="1:3">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A666" s="10" t="s">
         <v>107</v>
       </c>
@@ -8311,7 +8342,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="667" spans="1:3">
+    <row r="667" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A667" s="10" t="s">
         <v>47</v>
       </c>
@@ -8322,7 +8353,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="668" spans="1:3">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A668" s="10" t="s">
         <v>108</v>
       </c>
@@ -8331,6 +8362,1422 @@
       </c>
       <c r="C668" s="8">
         <v>46143</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A669" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B669" s="13">
+        <v>1</v>
+      </c>
+      <c r="C669" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A670" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B670" s="13">
+        <v>1</v>
+      </c>
+      <c r="C670" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A671" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B671" s="13">
+        <v>1</v>
+      </c>
+      <c r="C671" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A672" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B672" s="13">
+        <v>1</v>
+      </c>
+      <c r="C672" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A673" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B673" s="13">
+        <v>1</v>
+      </c>
+      <c r="C673" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A674" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B674" s="13">
+        <v>1</v>
+      </c>
+      <c r="C674" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A675" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B675" s="13">
+        <v>1</v>
+      </c>
+      <c r="C675" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A676" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B676" s="13">
+        <v>1</v>
+      </c>
+      <c r="C676" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A677" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B677" s="13">
+        <v>1</v>
+      </c>
+      <c r="C677" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A678" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B678" s="13">
+        <v>1</v>
+      </c>
+      <c r="C678" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A679" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B679" s="13">
+        <v>1</v>
+      </c>
+      <c r="C679" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A680" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B680" s="13">
+        <v>1</v>
+      </c>
+      <c r="C680" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A681" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B681" s="13">
+        <v>1</v>
+      </c>
+      <c r="C681" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A682" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B682" s="13">
+        <v>1</v>
+      </c>
+      <c r="C682" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A683" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B683" s="13">
+        <v>1</v>
+      </c>
+      <c r="C683" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A684" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B684" s="13">
+        <v>1</v>
+      </c>
+      <c r="C684" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A685" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B685" s="13">
+        <v>1</v>
+      </c>
+      <c r="C685" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A686" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B686" s="13">
+        <v>1</v>
+      </c>
+      <c r="C686" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A687" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B687" s="13">
+        <v>1</v>
+      </c>
+      <c r="C687" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A688" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B688" s="13">
+        <v>1</v>
+      </c>
+      <c r="C688" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A689" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B689" s="13">
+        <v>1</v>
+      </c>
+      <c r="C689" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A690" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B690" s="13">
+        <v>1</v>
+      </c>
+      <c r="C690" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A691" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B691" s="13">
+        <v>1</v>
+      </c>
+      <c r="C691" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A692" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B692" s="13">
+        <v>1</v>
+      </c>
+      <c r="C692" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A693" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B693" s="13">
+        <v>1</v>
+      </c>
+      <c r="C693" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A694" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B694" s="13">
+        <v>1</v>
+      </c>
+      <c r="C694" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A695" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B695" s="13">
+        <v>1</v>
+      </c>
+      <c r="C695" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A696" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B696" s="13">
+        <v>1</v>
+      </c>
+      <c r="C696" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A697" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B697" s="13">
+        <v>1</v>
+      </c>
+      <c r="C697" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A698" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B698" s="13">
+        <v>1</v>
+      </c>
+      <c r="C698" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A699" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B699" s="13">
+        <v>1</v>
+      </c>
+      <c r="C699" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A700" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B700" s="13">
+        <v>1</v>
+      </c>
+      <c r="C700" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A701" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B701" s="13">
+        <v>1</v>
+      </c>
+      <c r="C701" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A702" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B702" s="13">
+        <v>1</v>
+      </c>
+      <c r="C702" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A703" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B703" s="13">
+        <v>1</v>
+      </c>
+      <c r="C703" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A704" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B704" s="13">
+        <v>1</v>
+      </c>
+      <c r="C704" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A705" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B705" s="13">
+        <v>1</v>
+      </c>
+      <c r="C705" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A706" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B706" s="13">
+        <v>1</v>
+      </c>
+      <c r="C706" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A707" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B707" s="15">
+        <v>1</v>
+      </c>
+      <c r="C707" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A708" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B708" s="13">
+        <v>1</v>
+      </c>
+      <c r="C708" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A709" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B709" s="13">
+        <v>1</v>
+      </c>
+      <c r="C709" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A710" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B710" s="13">
+        <v>1</v>
+      </c>
+      <c r="C710" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A711" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B711" s="13">
+        <v>1</v>
+      </c>
+      <c r="C711" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A712" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B712" s="13">
+        <v>1</v>
+      </c>
+      <c r="C712" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A713" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B713" s="13">
+        <v>1</v>
+      </c>
+      <c r="C713" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A714" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B714" s="13">
+        <v>1</v>
+      </c>
+      <c r="C714" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A715" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B715" s="13">
+        <v>1</v>
+      </c>
+      <c r="C715" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A716" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B716" s="13">
+        <v>1</v>
+      </c>
+      <c r="C716" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A717" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B717" s="13">
+        <v>1</v>
+      </c>
+      <c r="C717" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A718" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B718" s="15">
+        <v>1</v>
+      </c>
+      <c r="C718" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A719" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B719" s="13">
+        <v>1</v>
+      </c>
+      <c r="C719" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A720" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B720" s="15">
+        <v>1</v>
+      </c>
+      <c r="C720" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A721" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B721" s="13">
+        <v>1</v>
+      </c>
+      <c r="C721" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A722" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B722" s="13">
+        <v>1</v>
+      </c>
+      <c r="C722" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A723" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B723" s="15">
+        <v>1</v>
+      </c>
+      <c r="C723" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A724" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B724" s="13">
+        <v>1</v>
+      </c>
+      <c r="C724" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A725" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B725" s="15">
+        <v>1</v>
+      </c>
+      <c r="C725" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A726" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B726" s="13">
+        <v>1</v>
+      </c>
+      <c r="C726" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A727" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B727" s="13">
+        <v>1</v>
+      </c>
+      <c r="C727" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A728" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B728" s="13">
+        <v>1</v>
+      </c>
+      <c r="C728" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A729" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B729" s="13">
+        <v>1</v>
+      </c>
+      <c r="C729" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A730" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B730" s="13">
+        <v>1</v>
+      </c>
+      <c r="C730" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A731" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B731" s="13">
+        <v>1</v>
+      </c>
+      <c r="C731" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A732" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B732" s="13">
+        <v>1</v>
+      </c>
+      <c r="C732" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A733" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B733" s="15">
+        <v>1</v>
+      </c>
+      <c r="C733" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A734" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B734" s="13">
+        <v>1</v>
+      </c>
+      <c r="C734" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A735" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B735" s="13">
+        <v>1</v>
+      </c>
+      <c r="C735" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A736" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B736" s="13">
+        <v>1</v>
+      </c>
+      <c r="C736" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A737" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B737" s="13">
+        <v>1</v>
+      </c>
+      <c r="C737" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A738" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B738" s="13">
+        <v>1</v>
+      </c>
+      <c r="C738" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A739" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B739" s="13">
+        <v>1</v>
+      </c>
+      <c r="C739" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A740" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B740" s="13">
+        <v>1</v>
+      </c>
+      <c r="C740" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A741" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B741" s="13">
+        <v>1</v>
+      </c>
+      <c r="C741" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A742" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B742" s="15">
+        <v>0.99151743638077283</v>
+      </c>
+      <c r="C742" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A743" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B743" s="13">
+        <v>1</v>
+      </c>
+      <c r="C743" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A744" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B744" s="13">
+        <v>1</v>
+      </c>
+      <c r="C744" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A745" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B745" s="13">
+        <v>1</v>
+      </c>
+      <c r="C745" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A746" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B746" s="13">
+        <v>1</v>
+      </c>
+      <c r="C746" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A747" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B747" s="13">
+        <v>1</v>
+      </c>
+      <c r="C747" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A748" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B748" s="13">
+        <v>1</v>
+      </c>
+      <c r="C748" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A749" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B749" s="13">
+        <v>1</v>
+      </c>
+      <c r="C749" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A750" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B750" s="13">
+        <v>1</v>
+      </c>
+      <c r="C750" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A751" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B751" s="13">
+        <v>1</v>
+      </c>
+      <c r="C751" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A752" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B752" s="13">
+        <v>1</v>
+      </c>
+      <c r="C752" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A753" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B753" s="13">
+        <v>1</v>
+      </c>
+      <c r="C753" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A754" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B754" s="13">
+        <v>1</v>
+      </c>
+      <c r="C754" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A755" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B755" s="13">
+        <v>1</v>
+      </c>
+      <c r="C755" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A756" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B756" s="13">
+        <v>1</v>
+      </c>
+      <c r="C756" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A757" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B757" s="13">
+        <v>1</v>
+      </c>
+      <c r="C757" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A758" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B758" s="13">
+        <v>1</v>
+      </c>
+      <c r="C758" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A759" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B759" s="13">
+        <v>1</v>
+      </c>
+      <c r="C759" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A760" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B760" s="13">
+        <v>1</v>
+      </c>
+      <c r="C760" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A761" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B761" s="13">
+        <v>1</v>
+      </c>
+      <c r="C761" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A762" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B762" s="13">
+        <v>1</v>
+      </c>
+      <c r="C762" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A763" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B763" s="13">
+        <v>1</v>
+      </c>
+      <c r="C763" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A764" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B764" s="13">
+        <v>1</v>
+      </c>
+      <c r="C764" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A765" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B765" s="13">
+        <v>1</v>
+      </c>
+      <c r="C765" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A766" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B766" s="13">
+        <v>1</v>
+      </c>
+      <c r="C766" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A767" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B767" s="13">
+        <v>1</v>
+      </c>
+      <c r="C767" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A768" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B768" s="13">
+        <v>1</v>
+      </c>
+      <c r="C768" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A769" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B769" s="13">
+        <v>1</v>
+      </c>
+      <c r="C769" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A770" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B770" s="13">
+        <v>1</v>
+      </c>
+      <c r="C770" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A771" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B771" s="13">
+        <v>1</v>
+      </c>
+      <c r="C771" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A772" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B772" s="13">
+        <v>1</v>
+      </c>
+      <c r="C772" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A773" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B773" s="13">
+        <v>1</v>
+      </c>
+      <c r="C773" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A774" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B774" s="13">
+        <v>1</v>
+      </c>
+      <c r="C774" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A775" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B775" s="13">
+        <v>1</v>
+      </c>
+      <c r="C775" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A776" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B776" s="13">
+        <v>1</v>
+      </c>
+      <c r="C776" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A777" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B777" s="13">
+        <v>1</v>
+      </c>
+      <c r="C777" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A778" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B778" s="13">
+        <v>1</v>
+      </c>
+      <c r="C778" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A779" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B779" s="13">
+        <v>1</v>
+      </c>
+      <c r="C779" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A780" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B780" s="13">
+        <v>1</v>
+      </c>
+      <c r="C780" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A781" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B781" s="13">
+        <v>1</v>
+      </c>
+      <c r="C781" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A782" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B782" s="13">
+        <v>1</v>
+      </c>
+      <c r="C782" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A783" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B783" s="13">
+        <v>1</v>
+      </c>
+      <c r="C783" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A784" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B784" s="13">
+        <v>1</v>
+      </c>
+      <c r="C784" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A785" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B785" s="13">
+        <v>1</v>
+      </c>
+      <c r="C785" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A786" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B786" s="13">
+        <v>1</v>
+      </c>
+      <c r="C786" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A787" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B787" s="13">
+        <v>1</v>
+      </c>
+      <c r="C787" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A788" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B788" s="13">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="C788" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A789" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B789" s="13">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="C789" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A790" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B790" s="13">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C790" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A791" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B791" s="13">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="C791" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A792" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B792" s="13">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="C792" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A793" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B793" s="13">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="C793" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A794" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B794" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="C794" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A795" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B795" s="15">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C795" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A796" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B796" s="13">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="C796" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B797" s="15">
+        <v>0.99536060733867571</v>
+      </c>
+      <c r="C797" s="8">
+        <v>46174</v>
       </c>
     </row>
   </sheetData>
